--- a/dist/greggs_model.xlsx
+++ b/dist/greggs_model.xlsx
@@ -683,7 +683,7 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>FINANCING ASSUMPTION: the revolving credit facility is assumed to be upsized. Forecast borrowings peak in FY2028 in every scenario, at roughly twice the £100m facility drawn against at FY2025. Peak-year leverage stays modest at 0.4x-0.6x EBITDA, so the upsize is an assumption about facility availability, not about solvency.</t>
+          <t>FINANCING ASSUMPTION: the revolving credit facility is assumed to be upsized. Forecast borrowings peak in FY2028 in every scenario, at roughly twice the £100m facility drawn against at FY2025. Lease-inclusive net debt peaks at 1.5x EBITDA in the Base case and 1.8x in Bear, so the upsize is an assumption about facility availability, not about solvency. That is the lease-consistent measure: against a post-IFRS 16 EBITDA, gross borrowings alone would read 0.5x, which flatters the position by excluding the lease obligations the denominator has already been credited for. Both figures are on the Checks sheet.</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3108,11 +3108,11 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>Peak borrowings are an assumed facility upsize, not a solvency problem: peak-year borrowings / EBITDA below 1.0x</t>
+          <t>Peak borrowings are an assumed facility upsize, not a solvency problem: lease-inclusive net debt / EBITDA below 2.0x every year</t>
         </is>
       </c>
       <c r="D10" s="2">
-        <f>AND('Schedules'!F47/'IS'!F7&lt;1.0,'Schedules'!G47/'IS'!G7&lt;1.0,'Schedules'!H47/'IS'!H7&lt;1.0,'Schedules'!I47/'IS'!I7&lt;1.0,'Schedules'!J47/'IS'!J7&lt;1.0)</f>
+        <f>AND(('Schedules'!F47-'Schedules'!F48+'Schedules'!F31)/'IS'!F7&lt;2.0,('Schedules'!G47-'Schedules'!G48+'Schedules'!G31)/'IS'!G7&lt;2.0,('Schedules'!H47-'Schedules'!H48+'Schedules'!H31)/'IS'!H7&lt;2.0,('Schedules'!I47-'Schedules'!I48+'Schedules'!I31)/'IS'!I7&lt;2.0,('Schedules'!J47-'Schedules'!J48+'Schedules'!J31)/'IS'!J7&lt;2.0)</f>
         <v/>
       </c>
     </row>
@@ -3137,23 +3137,34 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Peak borrowings / that year's EBITDA (x)</t>
+          <t>Peak lease-inclusive net debt / EBITDA (x) — the basis the check uses</t>
         </is>
       </c>
       <c r="C14" s="4">
+        <f>MAX(('Schedules'!F47-'Schedules'!F48+'Schedules'!F31)/'IS'!F7,('Schedules'!G47-'Schedules'!G48+'Schedules'!G31)/'IS'!G7,('Schedules'!H47-'Schedules'!H48+'Schedules'!H31)/'IS'!H7,('Schedules'!I47-'Schedules'!I48+'Schedules'!I31)/'IS'!I7,('Schedules'!J47-'Schedules'!J48+'Schedules'!J31)/'IS'!J7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Memo: peak gross borrowings / EBITDA (x) — the flattering basis, shown so the difference is visible rather than hidden</t>
+        </is>
+      </c>
+      <c r="C15" s="4">
         <f>MAX('Schedules'!F47/'IS'!F7,'Schedules'!G47/'IS'!G7,'Schedules'!H47/'IS'!H7,'Schedules'!I47/'IS'!I7,'Schedules'!J47/'IS'!J7)</f>
         <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Every result above is a live formula reading the rows it tests, not a recorded outcome. Move the scenario switch on Assumptions and they re-evaluate. If any reads FALSE, the workbook is not internally consistent and nothing downstream of it should be quoted.</t>
-        </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
+        <is>
+          <t>Every result above is a live formula reading the rows it tests, not a recorded outcome. Move the scenario switch on Assumptions and they re-evaluate. If any reads FALSE, the workbook is not internally consistent and nothing downstream of it should be quoted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>These test internal consistency, not whether the forecast is right. A model can tie out perfectly and still be built on the wrong drivers — the Cover's disclosures and the Historicals' source column are where that question is answered.</t>
         </is>

--- a/dist/greggs_model.xlsx
+++ b/dist/greggs_model.xlsx
@@ -80,9 +80,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -659,36 +662,37 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
+    <row r="2"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>All figures £m unless stated. Reported figures are post-IFRS 16.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Scenario switch: Assumptions!C3 (Bear / Base / Bull). Changing it re-drives every forecast, schedule and valuation in this workbook.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
+    <row r="5" ht="45" customHeight="1">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>There are no circular references: interest on borrowings is charged on the opening balance, so the workbook recalculates in a single pass. Iterative calculation is enabled anyway (100 iterations, 0.0001 delta) so that a later edit introducing a circularity converges rather than erroring.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
+    <row r="6" ht="105" customHeight="1">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>FINANCING ASSUMPTION: the revolving credit facility is assumed to be upsized. Forecast borrowings peak in FY2028 in every scenario, at roughly twice the £100m facility drawn against at FY2025. Lease-inclusive net debt peaks at 1.5x EBITDA in the Base case and 1.8x in Bear, so the upsize is an assumption about facility availability, not about solvency. That is the lease-consistent measure: against a post-IFRS 16 EBITDA, gross borrowings alone would read 0.5x, which flatters the position by excluding the lease obligations the denominator has already been credited for. Both figures are on the Checks sheet.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
+    <row r="7" ht="45" customHeight="1">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>The risk-free rate, equity risk premium, beta and RCF credit spread are reasoned judgement estimates, not sourced figures. Every other input is either transcribed from a filing (see Historicals, column L) or derived from those transcriptions.</t>
         </is>
@@ -742,23 +746,23 @@
           <t>Perpetuity growth (across)</t>
         </is>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="10">
         <f>'DCF'!$C$21-0.005</f>
         <v/>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="10">
         <f>'DCF'!$C$21-0.0025</f>
         <v/>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="10">
         <f>'DCF'!$C$21</f>
         <v/>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="10">
         <f>'DCF'!$C$21+0.0025</f>
         <v/>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="10">
         <f>'DCF'!$C$21+0.005</f>
         <v/>
       </c>
@@ -769,27 +773,27 @@
           <t>WACC less 100bp</t>
         </is>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <f>'DCF'!$C$5-0.01</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <f>('DCF'!$F$14/(1+$C5)^'DCF'!$F$15+'DCF'!$G$14/(1+$C5)^'DCF'!$G$15+'DCF'!$H$14/(1+$C5)^'DCF'!$H$15+'DCF'!$I$14/(1+$C5)^'DCF'!$I$15+'DCF'!$J$14/(1+$C5)^'DCF'!$J$15+('Sensitivity'!D26*(1+D$4)/($C5-D$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!D27*(1-'Assumptions'!$C$37)/(1+$C5)/(1-(1-'Assumptions'!$C$37)/(1+$C5)))/(1+$C5)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="18">
         <f>('DCF'!$F$14/(1+$C5)^'DCF'!$F$15+'DCF'!$G$14/(1+$C5)^'DCF'!$G$15+'DCF'!$H$14/(1+$C5)^'DCF'!$H$15+'DCF'!$I$14/(1+$C5)^'DCF'!$I$15+'DCF'!$J$14/(1+$C5)^'DCF'!$J$15+('Sensitivity'!E26*(1+E$4)/($C5-E$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!E27*(1-'Assumptions'!$C$37)/(1+$C5)/(1-(1-'Assumptions'!$C$37)/(1+$C5)))/(1+$C5)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="18">
         <f>('DCF'!$F$14/(1+$C5)^'DCF'!$F$15+'DCF'!$G$14/(1+$C5)^'DCF'!$G$15+'DCF'!$H$14/(1+$C5)^'DCF'!$H$15+'DCF'!$I$14/(1+$C5)^'DCF'!$I$15+'DCF'!$J$14/(1+$C5)^'DCF'!$J$15+('Sensitivity'!F26*(1+F$4)/($C5-F$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!F27*(1-'Assumptions'!$C$37)/(1+$C5)/(1-(1-'Assumptions'!$C$37)/(1+$C5)))/(1+$C5)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="18">
         <f>('DCF'!$F$14/(1+$C5)^'DCF'!$F$15+'DCF'!$G$14/(1+$C5)^'DCF'!$G$15+'DCF'!$H$14/(1+$C5)^'DCF'!$H$15+'DCF'!$I$14/(1+$C5)^'DCF'!$I$15+'DCF'!$J$14/(1+$C5)^'DCF'!$J$15+('Sensitivity'!G26*(1+G$4)/($C5-G$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!G27*(1-'Assumptions'!$C$37)/(1+$C5)/(1-(1-'Assumptions'!$C$37)/(1+$C5)))/(1+$C5)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="18">
         <f>('DCF'!$F$14/(1+$C5)^'DCF'!$F$15+'DCF'!$G$14/(1+$C5)^'DCF'!$G$15+'DCF'!$H$14/(1+$C5)^'DCF'!$H$15+'DCF'!$I$14/(1+$C5)^'DCF'!$I$15+'DCF'!$J$14/(1+$C5)^'DCF'!$J$15+('Sensitivity'!H26*(1+H$4)/($C5-H$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!H27*(1-'Assumptions'!$C$37)/(1+$C5)/(1-(1-'Assumptions'!$C$37)/(1+$C5)))/(1+$C5)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
@@ -800,27 +804,27 @@
           <t>WACC less 50bp</t>
         </is>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="10">
         <f>'DCF'!$C$5-0.005</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="18">
         <f>('DCF'!$F$14/(1+$C6)^'DCF'!$F$15+'DCF'!$G$14/(1+$C6)^'DCF'!$G$15+'DCF'!$H$14/(1+$C6)^'DCF'!$H$15+'DCF'!$I$14/(1+$C6)^'DCF'!$I$15+'DCF'!$J$14/(1+$C6)^'DCF'!$J$15+('Sensitivity'!D26*(1+D$4)/($C6-D$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!D27*(1-'Assumptions'!$C$37)/(1+$C6)/(1-(1-'Assumptions'!$C$37)/(1+$C6)))/(1+$C6)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="18">
         <f>('DCF'!$F$14/(1+$C6)^'DCF'!$F$15+'DCF'!$G$14/(1+$C6)^'DCF'!$G$15+'DCF'!$H$14/(1+$C6)^'DCF'!$H$15+'DCF'!$I$14/(1+$C6)^'DCF'!$I$15+'DCF'!$J$14/(1+$C6)^'DCF'!$J$15+('Sensitivity'!E26*(1+E$4)/($C6-E$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!E27*(1-'Assumptions'!$C$37)/(1+$C6)/(1-(1-'Assumptions'!$C$37)/(1+$C6)))/(1+$C6)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="18">
         <f>('DCF'!$F$14/(1+$C6)^'DCF'!$F$15+'DCF'!$G$14/(1+$C6)^'DCF'!$G$15+'DCF'!$H$14/(1+$C6)^'DCF'!$H$15+'DCF'!$I$14/(1+$C6)^'DCF'!$I$15+'DCF'!$J$14/(1+$C6)^'DCF'!$J$15+('Sensitivity'!F26*(1+F$4)/($C6-F$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!F27*(1-'Assumptions'!$C$37)/(1+$C6)/(1-(1-'Assumptions'!$C$37)/(1+$C6)))/(1+$C6)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="18">
         <f>('DCF'!$F$14/(1+$C6)^'DCF'!$F$15+'DCF'!$G$14/(1+$C6)^'DCF'!$G$15+'DCF'!$H$14/(1+$C6)^'DCF'!$H$15+'DCF'!$I$14/(1+$C6)^'DCF'!$I$15+'DCF'!$J$14/(1+$C6)^'DCF'!$J$15+('Sensitivity'!G26*(1+G$4)/($C6-G$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!G27*(1-'Assumptions'!$C$37)/(1+$C6)/(1-(1-'Assumptions'!$C$37)/(1+$C6)))/(1+$C6)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="18">
         <f>('DCF'!$F$14/(1+$C6)^'DCF'!$F$15+'DCF'!$G$14/(1+$C6)^'DCF'!$G$15+'DCF'!$H$14/(1+$C6)^'DCF'!$H$15+'DCF'!$I$14/(1+$C6)^'DCF'!$I$15+'DCF'!$J$14/(1+$C6)^'DCF'!$J$15+('Sensitivity'!H26*(1+H$4)/($C6-H$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!H27*(1-'Assumptions'!$C$37)/(1+$C6)/(1-(1-'Assumptions'!$C$37)/(1+$C6)))/(1+$C6)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
@@ -831,27 +835,27 @@
           <t>WACC (the model's own)</t>
         </is>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="10">
         <f>'DCF'!$C$5</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="18">
         <f>('DCF'!$F$14/(1+$C7)^'DCF'!$F$15+'DCF'!$G$14/(1+$C7)^'DCF'!$G$15+'DCF'!$H$14/(1+$C7)^'DCF'!$H$15+'DCF'!$I$14/(1+$C7)^'DCF'!$I$15+'DCF'!$J$14/(1+$C7)^'DCF'!$J$15+('Sensitivity'!D26*(1+D$4)/($C7-D$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!D27*(1-'Assumptions'!$C$37)/(1+$C7)/(1-(1-'Assumptions'!$C$37)/(1+$C7)))/(1+$C7)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="18">
         <f>('DCF'!$F$14/(1+$C7)^'DCF'!$F$15+'DCF'!$G$14/(1+$C7)^'DCF'!$G$15+'DCF'!$H$14/(1+$C7)^'DCF'!$H$15+'DCF'!$I$14/(1+$C7)^'DCF'!$I$15+'DCF'!$J$14/(1+$C7)^'DCF'!$J$15+('Sensitivity'!E26*(1+E$4)/($C7-E$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!E27*(1-'Assumptions'!$C$37)/(1+$C7)/(1-(1-'Assumptions'!$C$37)/(1+$C7)))/(1+$C7)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="18">
         <f>('DCF'!$F$14/(1+$C7)^'DCF'!$F$15+'DCF'!$G$14/(1+$C7)^'DCF'!$G$15+'DCF'!$H$14/(1+$C7)^'DCF'!$H$15+'DCF'!$I$14/(1+$C7)^'DCF'!$I$15+'DCF'!$J$14/(1+$C7)^'DCF'!$J$15+('Sensitivity'!F26*(1+F$4)/($C7-F$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!F27*(1-'Assumptions'!$C$37)/(1+$C7)/(1-(1-'Assumptions'!$C$37)/(1+$C7)))/(1+$C7)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="18">
         <f>('DCF'!$F$14/(1+$C7)^'DCF'!$F$15+'DCF'!$G$14/(1+$C7)^'DCF'!$G$15+'DCF'!$H$14/(1+$C7)^'DCF'!$H$15+'DCF'!$I$14/(1+$C7)^'DCF'!$I$15+'DCF'!$J$14/(1+$C7)^'DCF'!$J$15+('Sensitivity'!G26*(1+G$4)/($C7-G$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!G27*(1-'Assumptions'!$C$37)/(1+$C7)/(1-(1-'Assumptions'!$C$37)/(1+$C7)))/(1+$C7)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="18">
         <f>('DCF'!$F$14/(1+$C7)^'DCF'!$F$15+'DCF'!$G$14/(1+$C7)^'DCF'!$G$15+'DCF'!$H$14/(1+$C7)^'DCF'!$H$15+'DCF'!$I$14/(1+$C7)^'DCF'!$I$15+'DCF'!$J$14/(1+$C7)^'DCF'!$J$15+('Sensitivity'!H26*(1+H$4)/($C7-H$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!H27*(1-'Assumptions'!$C$37)/(1+$C7)/(1-(1-'Assumptions'!$C$37)/(1+$C7)))/(1+$C7)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
@@ -862,27 +866,27 @@
           <t>WACC plus 50bp</t>
         </is>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <f>'DCF'!$C$5+0.005</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <f>('DCF'!$F$14/(1+$C8)^'DCF'!$F$15+'DCF'!$G$14/(1+$C8)^'DCF'!$G$15+'DCF'!$H$14/(1+$C8)^'DCF'!$H$15+'DCF'!$I$14/(1+$C8)^'DCF'!$I$15+'DCF'!$J$14/(1+$C8)^'DCF'!$J$15+('Sensitivity'!D26*(1+D$4)/($C8-D$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!D27*(1-'Assumptions'!$C$37)/(1+$C8)/(1-(1-'Assumptions'!$C$37)/(1+$C8)))/(1+$C8)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="18">
         <f>('DCF'!$F$14/(1+$C8)^'DCF'!$F$15+'DCF'!$G$14/(1+$C8)^'DCF'!$G$15+'DCF'!$H$14/(1+$C8)^'DCF'!$H$15+'DCF'!$I$14/(1+$C8)^'DCF'!$I$15+'DCF'!$J$14/(1+$C8)^'DCF'!$J$15+('Sensitivity'!E26*(1+E$4)/($C8-E$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!E27*(1-'Assumptions'!$C$37)/(1+$C8)/(1-(1-'Assumptions'!$C$37)/(1+$C8)))/(1+$C8)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="18">
         <f>('DCF'!$F$14/(1+$C8)^'DCF'!$F$15+'DCF'!$G$14/(1+$C8)^'DCF'!$G$15+'DCF'!$H$14/(1+$C8)^'DCF'!$H$15+'DCF'!$I$14/(1+$C8)^'DCF'!$I$15+'DCF'!$J$14/(1+$C8)^'DCF'!$J$15+('Sensitivity'!F26*(1+F$4)/($C8-F$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!F27*(1-'Assumptions'!$C$37)/(1+$C8)/(1-(1-'Assumptions'!$C$37)/(1+$C8)))/(1+$C8)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="18">
         <f>('DCF'!$F$14/(1+$C8)^'DCF'!$F$15+'DCF'!$G$14/(1+$C8)^'DCF'!$G$15+'DCF'!$H$14/(1+$C8)^'DCF'!$H$15+'DCF'!$I$14/(1+$C8)^'DCF'!$I$15+'DCF'!$J$14/(1+$C8)^'DCF'!$J$15+('Sensitivity'!G26*(1+G$4)/($C8-G$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!G27*(1-'Assumptions'!$C$37)/(1+$C8)/(1-(1-'Assumptions'!$C$37)/(1+$C8)))/(1+$C8)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="18">
         <f>('DCF'!$F$14/(1+$C8)^'DCF'!$F$15+'DCF'!$G$14/(1+$C8)^'DCF'!$G$15+'DCF'!$H$14/(1+$C8)^'DCF'!$H$15+'DCF'!$I$14/(1+$C8)^'DCF'!$I$15+'DCF'!$J$14/(1+$C8)^'DCF'!$J$15+('Sensitivity'!H26*(1+H$4)/($C8-H$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!H27*(1-'Assumptions'!$C$37)/(1+$C8)/(1-(1-'Assumptions'!$C$37)/(1+$C8)))/(1+$C8)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
@@ -893,27 +897,27 @@
           <t>WACC plus 100bp</t>
         </is>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="10">
         <f>'DCF'!$C$5+0.01</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="18">
         <f>('DCF'!$F$14/(1+$C9)^'DCF'!$F$15+'DCF'!$G$14/(1+$C9)^'DCF'!$G$15+'DCF'!$H$14/(1+$C9)^'DCF'!$H$15+'DCF'!$I$14/(1+$C9)^'DCF'!$I$15+'DCF'!$J$14/(1+$C9)^'DCF'!$J$15+('Sensitivity'!D26*(1+D$4)/($C9-D$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!D27*(1-'Assumptions'!$C$37)/(1+$C9)/(1-(1-'Assumptions'!$C$37)/(1+$C9)))/(1+$C9)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="18">
         <f>('DCF'!$F$14/(1+$C9)^'DCF'!$F$15+'DCF'!$G$14/(1+$C9)^'DCF'!$G$15+'DCF'!$H$14/(1+$C9)^'DCF'!$H$15+'DCF'!$I$14/(1+$C9)^'DCF'!$I$15+'DCF'!$J$14/(1+$C9)^'DCF'!$J$15+('Sensitivity'!E26*(1+E$4)/($C9-E$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!E27*(1-'Assumptions'!$C$37)/(1+$C9)/(1-(1-'Assumptions'!$C$37)/(1+$C9)))/(1+$C9)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="18">
         <f>('DCF'!$F$14/(1+$C9)^'DCF'!$F$15+'DCF'!$G$14/(1+$C9)^'DCF'!$G$15+'DCF'!$H$14/(1+$C9)^'DCF'!$H$15+'DCF'!$I$14/(1+$C9)^'DCF'!$I$15+'DCF'!$J$14/(1+$C9)^'DCF'!$J$15+('Sensitivity'!F26*(1+F$4)/($C9-F$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!F27*(1-'Assumptions'!$C$37)/(1+$C9)/(1-(1-'Assumptions'!$C$37)/(1+$C9)))/(1+$C9)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="18">
         <f>('DCF'!$F$14/(1+$C9)^'DCF'!$F$15+'DCF'!$G$14/(1+$C9)^'DCF'!$G$15+'DCF'!$H$14/(1+$C9)^'DCF'!$H$15+'DCF'!$I$14/(1+$C9)^'DCF'!$I$15+'DCF'!$J$14/(1+$C9)^'DCF'!$J$15+('Sensitivity'!G26*(1+G$4)/($C9-G$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!G27*(1-'Assumptions'!$C$37)/(1+$C9)/(1-(1-'Assumptions'!$C$37)/(1+$C9)))/(1+$C9)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="18">
         <f>('DCF'!$F$14/(1+$C9)^'DCF'!$F$15+'DCF'!$G$14/(1+$C9)^'DCF'!$G$15+'DCF'!$H$14/(1+$C9)^'DCF'!$H$15+'DCF'!$I$14/(1+$C9)^'DCF'!$I$15+'DCF'!$J$14/(1+$C9)^'DCF'!$J$15+('Sensitivity'!H26*(1+H$4)/($C9-H$4)+'Assumptions'!$C$39*'Assumptions'!$C$37*'Sensitivity'!H27*(1-'Assumptions'!$C$37)/(1+$C9)/(1-(1-'Assumptions'!$C$37)/(1+$C9)))/(1+$C9)^'DCF'!$J$15-'DCF'!$C$61-'DCF'!$C$62)/'DCF'!$C$64*100</f>
         <v/>
       </c>
@@ -931,27 +935,27 @@
           <t>Implied terminal multiple at WACC less 100bp</t>
         </is>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="10">
         <f>'DCF'!$C$5-0.01</f>
         <v/>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <f>'Sensitivity'!D26*(1+D$4)/($C12-D$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <f>'Sensitivity'!E26*(1+E$4)/($C12-E$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <f>'Sensitivity'!F26*(1+F$4)/($C12-F$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="5">
         <f>'Sensitivity'!G26*(1+G$4)/($C12-G$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="5">
         <f>'Sensitivity'!H26*(1+H$4)/($C12-H$4)/'DCF'!$C$34</f>
         <v/>
       </c>
@@ -962,27 +966,27 @@
           <t>Implied terminal multiple at WACC less 50bp</t>
         </is>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="10">
         <f>'DCF'!$C$5-0.005</f>
         <v/>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <f>'Sensitivity'!D26*(1+D$4)/($C13-D$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="5">
         <f>'Sensitivity'!E26*(1+E$4)/($C13-E$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="5">
         <f>'Sensitivity'!F26*(1+F$4)/($C13-F$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="5">
         <f>'Sensitivity'!G26*(1+G$4)/($C13-G$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="5">
         <f>'Sensitivity'!H26*(1+H$4)/($C13-H$4)/'DCF'!$C$34</f>
         <v/>
       </c>
@@ -993,27 +997,27 @@
           <t>Implied terminal multiple at WACC (the model's own)</t>
         </is>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="10">
         <f>'DCF'!$C$5</f>
         <v/>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <f>'Sensitivity'!D26*(1+D$4)/($C14-D$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="5">
         <f>'Sensitivity'!E26*(1+E$4)/($C14-E$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="5">
         <f>'Sensitivity'!F26*(1+F$4)/($C14-F$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="5">
         <f>'Sensitivity'!G26*(1+G$4)/($C14-G$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="5">
         <f>'Sensitivity'!H26*(1+H$4)/($C14-H$4)/'DCF'!$C$34</f>
         <v/>
       </c>
@@ -1024,27 +1028,27 @@
           <t>Implied terminal multiple at WACC plus 50bp</t>
         </is>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="10">
         <f>'DCF'!$C$5+0.005</f>
         <v/>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="5">
         <f>'Sensitivity'!D26*(1+D$4)/($C15-D$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="5">
         <f>'Sensitivity'!E26*(1+E$4)/($C15-E$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="5">
         <f>'Sensitivity'!F26*(1+F$4)/($C15-F$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="5">
         <f>'Sensitivity'!G26*(1+G$4)/($C15-G$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="5">
         <f>'Sensitivity'!H26*(1+H$4)/($C15-H$4)/'DCF'!$C$34</f>
         <v/>
       </c>
@@ -1055,27 +1059,27 @@
           <t>Implied terminal multiple at WACC plus 100bp</t>
         </is>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="10">
         <f>'DCF'!$C$5+0.01</f>
         <v/>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <f>'Sensitivity'!D26*(1+D$4)/($C16-D$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <f>'Sensitivity'!E26*(1+E$4)/($C16-E$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="5">
         <f>'Sensitivity'!F26*(1+F$4)/($C16-F$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="5">
         <f>'Sensitivity'!G26*(1+G$4)/($C16-G$4)/'DCF'!$C$34</f>
         <v/>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="5">
         <f>'Sensitivity'!H26*(1+H$4)/($C16-H$4)/'DCF'!$C$34</f>
         <v/>
       </c>
@@ -1086,7 +1090,7 @@
           <t>For comparison: peer median EV/EBITDA (a TRAILING multiple, from Comps)</t>
         </is>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="16">
         <f>'Comps'!$J$17</f>
         <v/>
       </c>
@@ -1097,7 +1101,7 @@
           <t>For comparison: exit EV/EBITDA derived from the peer median EV/EBIT</t>
         </is>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="16">
         <f>'Comps'!$C$55</f>
         <v/>
       </c>
@@ -1115,23 +1119,23 @@
           <t>Terminal PP&amp;E / revenue (post-programme anchor at this growth rate)</t>
         </is>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="10">
         <f>('BS'!J3/'IS'!J3)/(1+D$4)^(1/'Assumptions'!$C$37)</f>
         <v/>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="10">
         <f>('BS'!J3/'IS'!J3)/(1+E$4)^(1/'Assumptions'!$C$37)</f>
         <v/>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="10">
         <f>('BS'!J3/'IS'!J3)/(1+F$4)^(1/'Assumptions'!$C$37)</f>
         <v/>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="10">
         <f>('BS'!J3/'IS'!J3)/(1+G$4)^(1/'Assumptions'!$C$37)</f>
         <v/>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="10">
         <f>('BS'!J3/'IS'!J3)/(1+H$4)^(1/'Assumptions'!$C$37)</f>
         <v/>
       </c>
@@ -1142,23 +1146,23 @@
           <t>Terminal total capex (% of revenue, sustaining at this growth rate)</t>
         </is>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="10">
         <f>'Sensitivity'!D21*(D$4+'Assumptions'!$C$37)/(1+D$4)/'Assumptions'!$C$59</f>
         <v/>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="10">
         <f>'Sensitivity'!E21*(E$4+'Assumptions'!$C$37)/(1+E$4)/'Assumptions'!$C$59</f>
         <v/>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="10">
         <f>'Sensitivity'!F21*(F$4+'Assumptions'!$C$37)/(1+F$4)/'Assumptions'!$C$59</f>
         <v/>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="10">
         <f>'Sensitivity'!G21*(G$4+'Assumptions'!$C$37)/(1+G$4)/'Assumptions'!$C$59</f>
         <v/>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="10">
         <f>'Sensitivity'!H21*(H$4+'Assumptions'!$C$37)/(1+H$4)/'Assumptions'!$C$59</f>
         <v/>
       </c>
@@ -1169,23 +1173,23 @@
           <t>Terminal D&amp;A (% of revenue: PP&amp;E + ROU depreciation + amortisation)</t>
         </is>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="10">
         <f>'Assumptions'!$C$37*'Sensitivity'!D21/(1+D$4)+'Assumptions'!$C$38*'DCF'!$C$23/(1+D$4)+'Sensitivity'!D22*'Assumptions'!$C$58*'Assumptions'!$C$60/(D$4+'Assumptions'!$C$60)</f>
         <v/>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="10">
         <f>'Assumptions'!$C$37*'Sensitivity'!E21/(1+E$4)+'Assumptions'!$C$38*'DCF'!$C$23/(1+E$4)+'Sensitivity'!E22*'Assumptions'!$C$58*'Assumptions'!$C$60/(E$4+'Assumptions'!$C$60)</f>
         <v/>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="10">
         <f>'Assumptions'!$C$37*'Sensitivity'!F21/(1+F$4)+'Assumptions'!$C$38*'DCF'!$C$23/(1+F$4)+'Sensitivity'!F22*'Assumptions'!$C$58*'Assumptions'!$C$60/(F$4+'Assumptions'!$C$60)</f>
         <v/>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="10">
         <f>'Assumptions'!$C$37*'Sensitivity'!G21/(1+G$4)+'Assumptions'!$C$38*'DCF'!$C$23/(1+G$4)+'Sensitivity'!G22*'Assumptions'!$C$58*'Assumptions'!$C$60/(G$4+'Assumptions'!$C$60)</f>
         <v/>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="10">
         <f>'Assumptions'!$C$37*'Sensitivity'!H21/(1+H$4)+'Assumptions'!$C$38*'DCF'!$C$23/(1+H$4)+'Sensitivity'!H22*'Assumptions'!$C$58*'Assumptions'!$C$60/(H$4+'Assumptions'!$C$60)</f>
         <v/>
       </c>
@@ -1196,23 +1200,23 @@
           <t>Terminal depreciation and amortisation</t>
         </is>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="4">
         <f>'Sensitivity'!D23*'DCF'!$C$32</f>
         <v/>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="4">
         <f>'Sensitivity'!E23*'DCF'!$C$32</f>
         <v/>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="4">
         <f>'Sensitivity'!F23*'DCF'!$C$32</f>
         <v/>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="4">
         <f>'Sensitivity'!G23*'DCF'!$C$32</f>
         <v/>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="4">
         <f>'Sensitivity'!H23*'DCF'!$C$32</f>
         <v/>
       </c>
@@ -1223,23 +1227,23 @@
           <t>Terminal EBIT (terminal EBITDA less the D&amp;A above)</t>
         </is>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="4">
         <f>'DCF'!$C$34-'Sensitivity'!D24</f>
         <v/>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="4">
         <f>'DCF'!$C$34-'Sensitivity'!E24</f>
         <v/>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="4">
         <f>'DCF'!$C$34-'Sensitivity'!F24</f>
         <v/>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="4">
         <f>'DCF'!$C$34-'Sensitivity'!G24</f>
         <v/>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="4">
         <f>'DCF'!$C$34-'Sensitivity'!H24</f>
         <v/>
       </c>
@@ -1250,23 +1254,23 @@
           <t>Terminal unlevered free cash flow</t>
         </is>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="4">
         <f>'Sensitivity'!D25*(1-'Assumptions'!$C$39)+'Sensitivity'!D24-'Sensitivity'!D22*'DCF'!$C$32-'DCF'!$C$23*(D$4+'Assumptions'!$C$38)/(1+D$4)*'DCF'!$C$32-'DCF'!$C$31*D$4/(1+D$4)*'DCF'!$C$32</f>
         <v/>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="4">
         <f>'Sensitivity'!E25*(1-'Assumptions'!$C$39)+'Sensitivity'!E24-'Sensitivity'!E22*'DCF'!$C$32-'DCF'!$C$23*(E$4+'Assumptions'!$C$38)/(1+E$4)*'DCF'!$C$32-'DCF'!$C$31*E$4/(1+E$4)*'DCF'!$C$32</f>
         <v/>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="4">
         <f>'Sensitivity'!F25*(1-'Assumptions'!$C$39)+'Sensitivity'!F24-'Sensitivity'!F22*'DCF'!$C$32-'DCF'!$C$23*(F$4+'Assumptions'!$C$38)/(1+F$4)*'DCF'!$C$32-'DCF'!$C$31*F$4/(1+F$4)*'DCF'!$C$32</f>
         <v/>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="4">
         <f>'Sensitivity'!G25*(1-'Assumptions'!$C$39)+'Sensitivity'!G24-'Sensitivity'!G22*'DCF'!$C$32-'DCF'!$C$23*(G$4+'Assumptions'!$C$38)/(1+G$4)*'DCF'!$C$32-'DCF'!$C$31*G$4/(1+G$4)*'DCF'!$C$32</f>
         <v/>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="4">
         <f>'Sensitivity'!H25*(1-'Assumptions'!$C$39)+'Sensitivity'!H24-'Sensitivity'!H22*'DCF'!$C$32-'DCF'!$C$23*(H$4+'Assumptions'!$C$38)/(1+H$4)*'DCF'!$C$32-'DCF'!$C$31*H$4/(1+H$4)*'DCF'!$C$32</f>
         <v/>
       </c>
@@ -1277,23 +1281,23 @@
           <t>Excess PP&amp;E over this growth rate's re-based base, at FY2029</t>
         </is>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="4">
         <f>'BS'!I3-'Sensitivity'!D21*'IS'!I3</f>
         <v/>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="4">
         <f>'BS'!I3-'Sensitivity'!E21*'IS'!I3</f>
         <v/>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="4">
         <f>'BS'!I3-'Sensitivity'!F21*'IS'!I3</f>
         <v/>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="4">
         <f>'BS'!I3-'Sensitivity'!G21*'IS'!I3</f>
         <v/>
       </c>
-      <c r="H27" s="3">
+      <c r="H27" s="4">
         <f>'BS'!I3-'Sensitivity'!H21*'IS'!I3</f>
         <v/>
       </c>
@@ -1304,7 +1308,7 @@
           <t>Check: centre column's terminal FCF less the DCF's own (must be nil)</t>
         </is>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="4">
         <f>'Sensitivity'!F26-'DCF'!$C$40</f>
         <v/>
       </c>
@@ -1345,42 +1349,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>SSP Group</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Domino's Pizza Group</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>J D Wetherspoon</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Mitchells &amp; Butlers</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Whitbread</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>Peer min</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Peer median</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>Peer max</t>
         </is>
@@ -1392,19 +1396,19 @@
           <t>Share price (pence)</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n">
+      <c r="C3" s="19" t="n">
         <v>212.4</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="19" t="n">
         <v>218</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="19" t="n">
         <v>814</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="19" t="n">
         <v>284.5</v>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="19" t="n">
         <v>2493</v>
       </c>
     </row>
@@ -1414,19 +1418,19 @@
           <t>Shares outstanding (m)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="11" t="n">
         <v>762.24</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="11" t="n">
         <v>381.16</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="11" t="n">
         <v>102.79</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="11" t="n">
         <v>593.9299999999999</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="11" t="n">
         <v>167.14</v>
       </c>
     </row>
@@ -1436,19 +1440,19 @@
           <t>Market capitalisation (£m)</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <v>1618.998</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>830.929</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="12" t="n">
         <v>836.711</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="12" t="n">
         <v>1689.731</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="12" t="n">
         <v>4166.8</v>
       </c>
     </row>
@@ -1458,19 +1462,19 @@
           <t>Net debt including lease liabilities (£m)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>1816.9</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>524.7</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>1129.1</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>1277</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="12" t="n">
         <v>5232</v>
       </c>
     </row>
@@ -1480,19 +1484,19 @@
           <t xml:space="preserve">  of which lease liabilities (£m)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>1242.7</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>240.1</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>407.2</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>434</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="12" t="n">
         <v>4523.1</v>
       </c>
     </row>
@@ -1502,19 +1506,19 @@
           <t>Minority interests (£m, book value)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>186.8</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1524,19 +1528,19 @@
           <t>Enterprise value (£m)</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>3622.698</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>1355.029</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <v>1965.811</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="12" t="n">
         <v>2966.731</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="12" t="n">
         <v>9398.799999999999</v>
       </c>
     </row>
@@ -1546,19 +1550,19 @@
           <t>EBITDA (£m, post-IFRS 16, underlying)</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <v>687.2</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>133.9</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>260.8</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="12" t="n">
         <v>465</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="12" t="n">
         <v>1076</v>
       </c>
     </row>
@@ -1568,19 +1572,19 @@
           <t>EBIT (£m, post-IFRS 16, underlying)</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="12" t="n">
         <v>269.1</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>111.2</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="12" t="n">
         <v>146.4</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="12" t="n">
         <v>330</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="12" t="n">
         <v>649</v>
       </c>
     </row>
@@ -1590,19 +1594,19 @@
           <t>Net income (£m, statutory, attributable)</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <v>-74.40000000000001</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="12" t="n">
         <v>58.6</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="12" t="n">
         <v>212.9</v>
       </c>
     </row>
@@ -1612,23 +1616,23 @@
           <t>Check: price x shares less market capitalisation (£m, |x| &lt; 0.01)</t>
         </is>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="4">
         <f>'Comps'!C3/100*'Comps'!C4-'Comps'!C5</f>
         <v/>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="4">
         <f>'Comps'!D3/100*'Comps'!D4-'Comps'!D5</f>
         <v/>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="4">
         <f>'Comps'!E3/100*'Comps'!E4-'Comps'!E5</f>
         <v/>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="4">
         <f>'Comps'!F3/100*'Comps'!F4-'Comps'!F5</f>
         <v/>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="4">
         <f>'Comps'!G3/100*'Comps'!G4-'Comps'!G5</f>
         <v/>
       </c>
@@ -1639,23 +1643,23 @@
           <t>Check: market cap + net debt + minorities less EV (£m, |x| &lt; 0.01)</t>
         </is>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="4">
         <f>'Comps'!C5+'Comps'!C6+'Comps'!C8-'Comps'!C9</f>
         <v/>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="4">
         <f>'Comps'!D5+'Comps'!D6+'Comps'!D8-'Comps'!D9</f>
         <v/>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="4">
         <f>'Comps'!E5+'Comps'!E6+'Comps'!E8-'Comps'!E9</f>
         <v/>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="4">
         <f>'Comps'!F5+'Comps'!F6+'Comps'!F8-'Comps'!F9</f>
         <v/>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="4">
         <f>'Comps'!G5+'Comps'!G6+'Comps'!G8-'Comps'!G9</f>
         <v/>
       </c>
@@ -1666,23 +1670,23 @@
           <t>Implied D&amp;A (£m, EBITDA less EBIT)</t>
         </is>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="4">
         <f>'Comps'!C10-'Comps'!C11</f>
         <v/>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="4">
         <f>'Comps'!D10-'Comps'!D11</f>
         <v/>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="4">
         <f>'Comps'!E10-'Comps'!E11</f>
         <v/>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="4">
         <f>'Comps'!F10-'Comps'!F11</f>
         <v/>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="4">
         <f>'Comps'!G10-'Comps'!G11</f>
         <v/>
       </c>
@@ -1693,35 +1697,35 @@
           <t>D&amp;A / EBITDA (capital intensity)</t>
         </is>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="10">
         <f>('Comps'!C10-'Comps'!C11)/'Comps'!C10</f>
         <v/>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="10">
         <f>('Comps'!D10-'Comps'!D11)/'Comps'!D10</f>
         <v/>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10">
         <f>('Comps'!E10-'Comps'!E11)/'Comps'!E10</f>
         <v/>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="10">
         <f>('Comps'!F10-'Comps'!F11)/'Comps'!F10</f>
         <v/>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="10">
         <f>('Comps'!G10-'Comps'!G11)/'Comps'!G10</f>
         <v/>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="10">
         <f>MIN(C16:G16)</f>
         <v/>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="10">
         <f>MEDIAN(C16:G16)</f>
         <v/>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="10">
         <f>MAX(C16:G16)</f>
         <v/>
       </c>
@@ -1732,35 +1736,35 @@
           <t>EV / EBITDA</t>
         </is>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <f>'Comps'!C9/'Comps'!C10</f>
         <v/>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="5">
         <f>'Comps'!D9/'Comps'!D10</f>
         <v/>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="5">
         <f>'Comps'!E9/'Comps'!E10</f>
         <v/>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="5">
         <f>'Comps'!F9/'Comps'!F10</f>
         <v/>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="5">
         <f>'Comps'!G9/'Comps'!G10</f>
         <v/>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="5">
         <f>MIN(C17:G17)</f>
         <v/>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="5">
         <f>MEDIAN(C17:G17)</f>
         <v/>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="5">
         <f>MAX(C17:G17)</f>
         <v/>
       </c>
@@ -1771,35 +1775,35 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="5">
         <f>'Comps'!C9/'Comps'!C11</f>
         <v/>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="5">
         <f>'Comps'!D9/'Comps'!D11</f>
         <v/>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="5">
         <f>'Comps'!E9/'Comps'!E11</f>
         <v/>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="5">
         <f>'Comps'!F9/'Comps'!F11</f>
         <v/>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="5">
         <f>'Comps'!G9/'Comps'!G11</f>
         <v/>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="5">
         <f>MIN(C18:G18)</f>
         <v/>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="5">
         <f>MEDIAN(C18:G18)</f>
         <v/>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="5">
         <f>MAX(C18:G18)</f>
         <v/>
       </c>
@@ -1810,35 +1814,35 @@
           <t>P/E (SSP is a statutory loss and is excluded from the statistics)</t>
         </is>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="5">
         <f>'Comps'!C5/'Comps'!C12</f>
         <v/>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="5">
         <f>'Comps'!D5/'Comps'!D12</f>
         <v/>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="5">
         <f>'Comps'!E5/'Comps'!E12</f>
         <v/>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="5">
         <f>'Comps'!F5/'Comps'!F12</f>
         <v/>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="5">
         <f>'Comps'!G5/'Comps'!G12</f>
         <v/>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="5">
         <f>MIN(D19:G19)</f>
         <v/>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="5">
         <f>MEDIAN(D19:G19)</f>
         <v/>
       </c>
-      <c r="K19" s="4">
+      <c r="K19" s="5">
         <f>MAX(D19:G19)</f>
         <v/>
       </c>
@@ -1849,27 +1853,27 @@
           <t>Source (results announcement, then the price snapshot)</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>SSP Group plc, '2025 Full Year Results Announcement' RNS, 4 December 2025, year ended 30 September 2025; price stockanalysis.com LON:SSPG 5 August 2026 11:45 GMT</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Domino's Pizza Group plc, 'Full year results for the 52 weeks ended 28.12.25' RNS, 10 March 2026; price stockanalysis.com LON:DOM 5 August 2026 11:59 GMT</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>J D Wetherspoon plc, 'Preliminary Results' RNS, 3 October 2025, 52 weeks ended 27 July 2025; price stockanalysis.com LON:JDW 5 August 2026 11:54 GMT</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>Mitchells &amp; Butlers plc, 'Full Year Results' RNS, 28 November 2025, 52 weeks ended 27 September 2025; price stockanalysis.com LON:MAB 5 August 2026 11:52 GMT</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>Whitbread PLC, 'Preliminary Results Announcement' RNS, 30 April 2026, 52 weeks ended 26 February 2026; price stockanalysis.com LON:WTB 5 August 2026 11:58 GMT</t>
         </is>
@@ -1886,7 +1890,7 @@
           <t>All six share prices were observed at</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>5 August 2026, 11:45-11:59 GMT</t>
         </is>
@@ -1905,7 +1909,7 @@
           <t>Greggs share price (pence)</t>
         </is>
       </c>
-      <c r="C24" s="18" t="n">
+      <c r="C24" s="19" t="n">
         <v>1964</v>
       </c>
     </row>
@@ -1915,7 +1919,7 @@
           <t>Greggs shares outstanding (m, price provider; the filing's diluted count is on Historicals)</t>
         </is>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C25" s="11" t="n">
         <v>101.96</v>
       </c>
     </row>
@@ -1925,7 +1929,7 @@
           <t>Greggs market capitalisation (£m)</t>
         </is>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="4">
         <f>'Comps'!$C$24/100*'Comps'!$C$25</f>
         <v/>
       </c>
@@ -1936,7 +1940,7 @@
           <t>Greggs net debt including lease liabilities (£m, FY2025 actual)</t>
         </is>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="4">
         <f>'Historicals'!E31-'Historicals'!E25+'Historicals'!E30</f>
         <v/>
       </c>
@@ -1947,7 +1951,7 @@
           <t>Greggs enterprise value (£m)</t>
         </is>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="4">
         <f>'Comps'!$C$26+'Comps'!$C$27</f>
         <v/>
       </c>
@@ -1958,7 +1962,7 @@
           <t>Greggs EBITDA (£m, FY2025, the basis the model forecasts)</t>
         </is>
       </c>
-      <c r="C29" s="13">
+      <c r="C29" s="14">
         <f>'Historicals'!E13</f>
         <v/>
       </c>
@@ -1969,7 +1973,7 @@
           <t>Greggs EBIT (£m, FY2025, struck AFTER impairment — see below)</t>
         </is>
       </c>
-      <c r="C30" s="13">
+      <c r="C30" s="14">
         <f>'Historicals'!E15</f>
         <v/>
       </c>
@@ -1980,7 +1984,7 @@
           <t>Greggs net income (£m, FY2025)</t>
         </is>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="14">
         <f>'Historicals'!E17</f>
         <v/>
       </c>
@@ -1991,7 +1995,7 @@
           <t>Greggs EV / EBITDA</t>
         </is>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="5">
         <f>'Comps'!$C$28/'Comps'!$C$29</f>
         <v/>
       </c>
@@ -2002,7 +2006,7 @@
           <t>Greggs EV / EBIT</t>
         </is>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="5">
         <f>'Comps'!$C$28/'Comps'!$C$30</f>
         <v/>
       </c>
@@ -2013,7 +2017,7 @@
           <t>Greggs P/E</t>
         </is>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="5">
         <f>'Comps'!$C$26/'Comps'!$C$31</f>
         <v/>
       </c>
@@ -2024,7 +2028,7 @@
           <t>Discount to the peer median on EV/EBITDA (negative = cheaper)</t>
         </is>
       </c>
-      <c r="C35" s="9">
+      <c r="C35" s="10">
         <f>'Comps'!$C$32/'Comps'!$J$17-1</f>
         <v/>
       </c>
@@ -2035,7 +2039,7 @@
           <t>Discount to the peer median on EV/EBIT (NOT like for like — see impairment below)</t>
         </is>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="10">
         <f>'Comps'!$C$33/'Comps'!$J$18-1</f>
         <v/>
       </c>
@@ -2053,7 +2057,7 @@
           <t>FY2025 net impairment of PP&amp;E, inside depreciation (FY2025 AR p.148)</t>
         </is>
       </c>
-      <c r="C39" s="11" t="n">
+      <c r="C39" s="12" t="n">
         <v>3.9</v>
       </c>
     </row>
@@ -2063,7 +2067,7 @@
           <t>FY2025 net impairment of ROU assets, inside depreciation (FY2025 AR p.148)</t>
         </is>
       </c>
-      <c r="C40" s="11" t="n">
+      <c r="C40" s="12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2073,7 +2077,7 @@
           <t>FY2025 net impairment inside D&amp;A (£m)</t>
         </is>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="4">
         <f>'Comps'!$C$39+'Comps'!$C$40</f>
         <v/>
       </c>
@@ -2084,7 +2088,7 @@
           <t>Greggs EBIT on the peers' basis, before impairment (£m)</t>
         </is>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="4">
         <f>'Comps'!$C$30+'Comps'!$C$41</f>
         <v/>
       </c>
@@ -2095,7 +2099,7 @@
           <t>Peers'-basis EV / EBIT (Greggs, before impairment)</t>
         </is>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="5">
         <f>'Comps'!$C$28/'Comps'!$C$42</f>
         <v/>
       </c>
@@ -2106,7 +2110,7 @@
           <t>Discount to the peer median on the peers'-basis EV/EBIT (the like-for-like read)</t>
         </is>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="10">
         <f>'Comps'!$C$43/'Comps'!$J$18-1</f>
         <v/>
       </c>
@@ -2124,7 +2128,7 @@
           <t>Comps-implied share price at the peer minimum EV/EBITDA (p)</t>
         </is>
       </c>
-      <c r="C47" s="17">
+      <c r="C47" s="18">
         <f>('Comps'!$C$29*'Comps'!$I$17-('Historicals'!E31-'Historicals'!E25)-'Historicals'!E30)/'Historicals'!E44*100</f>
         <v/>
       </c>
@@ -2135,7 +2139,7 @@
           <t>Comps-implied share price at the peer median EV/EBITDA (p)</t>
         </is>
       </c>
-      <c r="C48" s="17">
+      <c r="C48" s="18">
         <f>('Comps'!$C$29*'Comps'!$J$17-('Historicals'!E31-'Historicals'!E25)-'Historicals'!E30)/'Historicals'!E44*100</f>
         <v/>
       </c>
@@ -2146,7 +2150,7 @@
           <t>Comps-implied share price at the peer maximum EV/EBITDA (p)</t>
         </is>
       </c>
-      <c r="C49" s="17">
+      <c r="C49" s="18">
         <f>('Comps'!$C$29*'Comps'!$K$17-('Historicals'!E31-'Historicals'!E25)-'Historicals'!E30)/'Historicals'!E44*100</f>
         <v/>
       </c>
@@ -2157,7 +2161,7 @@
           <t>52-week low (pence, market observation, no formula source)</t>
         </is>
       </c>
-      <c r="C50" s="18" t="n">
+      <c r="C50" s="19" t="n">
         <v>1407.2</v>
       </c>
     </row>
@@ -2167,7 +2171,7 @@
           <t>52-week high (pence, market observation, no formula source)</t>
         </is>
       </c>
-      <c r="C51" s="18" t="n">
+      <c r="C51" s="19" t="n">
         <v>2046</v>
       </c>
     </row>
@@ -2184,7 +2188,7 @@
           <t>Terminal D&amp;A / EBITDA, from the DCF's re-based terminal year</t>
         </is>
       </c>
-      <c r="C54" s="14">
+      <c r="C54" s="15">
         <f>'DCF'!$C$41</f>
         <v/>
       </c>
@@ -2195,7 +2199,7 @@
           <t>Derived exit EV/EBITDA (= peer median EV/EBIT x (1 - terminal D&amp;A/EBITDA))</t>
         </is>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="5">
         <f>'Comps'!$J$18*(1-'Comps'!$C$54)</f>
         <v/>
       </c>
@@ -2206,7 +2210,7 @@
           <t>Exit EV/EBITDA as shipped on Assumptions (the derived figure, 2dp)</t>
         </is>
       </c>
-      <c r="C56" s="15">
+      <c r="C56" s="16">
         <f>'Assumptions'!$C$31</f>
         <v/>
       </c>
@@ -2217,7 +2221,7 @@
           <t>Rounding carried by the shipped driver (derived less shipped)</t>
         </is>
       </c>
-      <c r="C57" s="12">
+      <c r="C57" s="13">
         <f>'Comps'!$C$55-'Comps'!$C$56</f>
         <v/>
       </c>
@@ -2279,23 +2283,23 @@
       </c>
     </row>
     <row r="2">
-      <c r="F2" s="5">
+      <c r="F2" s="6">
         <f>'Assumptions'!F$2</f>
         <v/>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <f>'Assumptions'!G$2</f>
         <v/>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="6">
         <f>'Assumptions'!H$2</f>
         <v/>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="6">
         <f>'Assumptions'!I$2</f>
         <v/>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="6">
         <f>'Assumptions'!J$2</f>
         <v/>
       </c>
@@ -2306,7 +2310,7 @@
           <t>Entry enterprise value (Greggs' traded EV from Comps)</t>
         </is>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="14">
         <f>'Comps'!$C$28</f>
         <v/>
       </c>
@@ -2317,7 +2321,7 @@
           <t>Entry EBITDA (FY2025, the basis the model forecasts)</t>
         </is>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="14">
         <f>'Historicals'!E13</f>
         <v/>
       </c>
@@ -2328,7 +2332,7 @@
           <t>Entry EV/EBITDA</t>
         </is>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <f>'LBO'!$C$3/'LBO'!$C$4</f>
         <v/>
       </c>
@@ -2339,7 +2343,7 @@
           <t>Entry leverage (x EBITDA, total net debt INCLUDING leases)</t>
         </is>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="16">
         <f>'Assumptions'!$C$64</f>
         <v/>
       </c>
@@ -2350,7 +2354,7 @@
           <t>Entry total net debt including leases</t>
         </is>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="4">
         <f>'LBO'!$C$6*'LBO'!$C$4</f>
         <v/>
       </c>
@@ -2361,7 +2365,7 @@
           <t xml:space="preserve">  of which the existing lease liability (already spoken for)</t>
         </is>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="14">
         <f>'Historicals'!E30</f>
         <v/>
       </c>
@@ -2372,7 +2376,7 @@
           <t xml:space="preserve">  new financial debt raised (the leverage less the leases)</t>
         </is>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="4">
         <f>'LBO'!$C$7-'LBO'!$C$8</f>
         <v/>
       </c>
@@ -2383,7 +2387,7 @@
           <t>Sponsor equity cheque (entry EV less total entry debt)</t>
         </is>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="4">
         <f>'LBO'!$C$3-'LBO'!$C$7</f>
         <v/>
       </c>
@@ -2401,23 +2405,23 @@
           <t>Unlevered free cash flow (the DCF's own, unchanged)</t>
         </is>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <f>'DCF'!F14</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="14">
         <f>'DCF'!G14</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="14">
         <f>'DCF'!H14</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="14">
         <f>'DCF'!I14</f>
         <v/>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="14">
         <f>'DCF'!J14</f>
         <v/>
       </c>
@@ -2428,23 +2432,23 @@
           <t>New ROU additions added back (a new lease funds its own asset)</t>
         </is>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <f>'Schedules'!F25</f>
         <v/>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="14">
         <f>'Schedules'!G25</f>
         <v/>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="14">
         <f>'Schedules'!H25</f>
         <v/>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="14">
         <f>'Schedules'!I25</f>
         <v/>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="14">
         <f>'Schedules'!J25</f>
         <v/>
       </c>
@@ -2455,23 +2459,23 @@
           <t>Lease principal repaid</t>
         </is>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <f>'Schedules'!F30</f>
         <v/>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="14">
         <f>'Schedules'!G30</f>
         <v/>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="14">
         <f>'Schedules'!H30</f>
         <v/>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="14">
         <f>'Schedules'!I30</f>
         <v/>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="14">
         <f>'Schedules'!J30</f>
         <v/>
       </c>
@@ -2482,23 +2486,23 @@
           <t>Lease interest</t>
         </is>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="14">
         <f>'Schedules'!F29</f>
         <v/>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="14">
         <f>'Schedules'!G29</f>
         <v/>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="14">
         <f>'Schedules'!H29</f>
         <v/>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="14">
         <f>'Schedules'!I29</f>
         <v/>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="14">
         <f>'Schedules'!J29</f>
         <v/>
       </c>
@@ -2509,23 +2513,23 @@
           <t>Opening financial debt</t>
         </is>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="4">
         <f>'LBO'!$C$9</f>
         <v/>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="4">
         <f>'LBO'!F20</f>
         <v/>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="4">
         <f>'LBO'!G20</f>
         <v/>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="4">
         <f>'LBO'!H20</f>
         <v/>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="4">
         <f>'LBO'!I20</f>
         <v/>
       </c>
@@ -2536,23 +2540,23 @@
           <t>Interest on financial debt (rate on the opening balance)</t>
         </is>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="4">
         <f>'LBO'!F17*'Assumptions'!$C$44</f>
         <v/>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="4">
         <f>'LBO'!G17*'Assumptions'!$C$44</f>
         <v/>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="4">
         <f>'LBO'!H17*'Assumptions'!$C$44</f>
         <v/>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="4">
         <f>'LBO'!I17*'Assumptions'!$C$44</f>
         <v/>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="4">
         <f>'LBO'!J17*'Assumptions'!$C$44</f>
         <v/>
       </c>
@@ -2563,23 +2567,23 @@
           <t>Cash available to repay debt (negative draws more)</t>
         </is>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="4">
         <f>'LBO'!F13+'LBO'!F14-'LBO'!F15-'LBO'!F16*(1-'Assumptions'!$C$39)-'LBO'!F18*(1-'Assumptions'!$C$39)</f>
         <v/>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="4">
         <f>'LBO'!G13+'LBO'!G14-'LBO'!G15-'LBO'!G16*(1-'Assumptions'!$C$39)-'LBO'!G18*(1-'Assumptions'!$C$39)</f>
         <v/>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="4">
         <f>'LBO'!H13+'LBO'!H14-'LBO'!H15-'LBO'!H16*(1-'Assumptions'!$C$39)-'LBO'!H18*(1-'Assumptions'!$C$39)</f>
         <v/>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="4">
         <f>'LBO'!I13+'LBO'!I14-'LBO'!I15-'LBO'!I16*(1-'Assumptions'!$C$39)-'LBO'!I18*(1-'Assumptions'!$C$39)</f>
         <v/>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="4">
         <f>'LBO'!J13+'LBO'!J14-'LBO'!J15-'LBO'!J16*(1-'Assumptions'!$C$39)-'LBO'!J18*(1-'Assumptions'!$C$39)</f>
         <v/>
       </c>
@@ -2590,23 +2594,23 @@
           <t>Closing financial debt</t>
         </is>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="4">
         <f>'LBO'!F17-'LBO'!F19</f>
         <v/>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="4">
         <f>'LBO'!G17-'LBO'!G19</f>
         <v/>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="4">
         <f>'LBO'!H17-'LBO'!H19</f>
         <v/>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="4">
         <f>'LBO'!I17-'LBO'!I19</f>
         <v/>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="4">
         <f>'LBO'!J17-'LBO'!J19</f>
         <v/>
       </c>
@@ -2617,23 +2621,23 @@
           <t>Closing lease liabilities (the DCF's own lease book — it GROWS)</t>
         </is>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="14">
         <f>'Schedules'!F31</f>
         <v/>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="14">
         <f>'Schedules'!G31</f>
         <v/>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="14">
         <f>'Schedules'!H31</f>
         <v/>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="14">
         <f>'Schedules'!I31</f>
         <v/>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="14">
         <f>'Schedules'!J31</f>
         <v/>
       </c>
@@ -2644,23 +2648,23 @@
           <t>Closing total debt including leases</t>
         </is>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="4">
         <f>'LBO'!F20+'LBO'!F21</f>
         <v/>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="4">
         <f>'LBO'!G20+'LBO'!G21</f>
         <v/>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="4">
         <f>'LBO'!H20+'LBO'!H21</f>
         <v/>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="4">
         <f>'LBO'!I20+'LBO'!I21</f>
         <v/>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="4">
         <f>'LBO'!J20+'LBO'!J21</f>
         <v/>
       </c>
@@ -2671,23 +2675,23 @@
           <t>Closing total debt / that year's EBITDA</t>
         </is>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="5">
         <f>'LBO'!F22/'IS'!F7</f>
         <v/>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="5">
         <f>'LBO'!G22/'IS'!G7</f>
         <v/>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="5">
         <f>'LBO'!H22/'IS'!H7</f>
         <v/>
       </c>
-      <c r="I23" s="4">
+      <c r="I23" s="5">
         <f>'LBO'!I22/'IS'!I7</f>
         <v/>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="5">
         <f>'LBO'!J22/'IS'!J7</f>
         <v/>
       </c>
@@ -2705,7 +2709,7 @@
           <t>Exit EBITDA (FY2030)</t>
         </is>
       </c>
-      <c r="C26" s="13">
+      <c r="C26" s="14">
         <f>'IS'!J7</f>
         <v/>
       </c>
@@ -2716,7 +2720,7 @@
           <t>Exit EV/EBITDA (the entry multiple, unchanged)</t>
         </is>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="5">
         <f>'LBO'!$C$5</f>
         <v/>
       </c>
@@ -2727,7 +2731,7 @@
           <t>Exit enterprise value</t>
         </is>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="4">
         <f>'LBO'!$C$27*'LBO'!$C$26</f>
         <v/>
       </c>
@@ -2738,7 +2742,7 @@
           <t>Exit total net debt including leases</t>
         </is>
       </c>
-      <c r="C29" s="13">
+      <c r="C29" s="14">
         <f>'LBO'!J22</f>
         <v/>
       </c>
@@ -2749,7 +2753,7 @@
           <t>Exit equity value</t>
         </is>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="4">
         <f>'LBO'!$C$28-'LBO'!$C$29</f>
         <v/>
       </c>
@@ -2760,7 +2764,7 @@
           <t>Hold period (years, = the length of the forecast)</t>
         </is>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="13">
         <f>COLUMNS(F13:J13)</f>
         <v/>
       </c>
@@ -2771,7 +2775,7 @@
           <t>Money multiple (exit equity / entry equity)</t>
         </is>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="5">
         <f>'LBO'!$C$30/'LBO'!$C$10</f>
         <v/>
       </c>
@@ -2782,7 +2786,7 @@
           <t>IRR (geometric: one cheque in, one out)</t>
         </is>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="10">
         <f>'LBO'!$C$32^(1/'LBO'!$C$31)-1</f>
         <v/>
       </c>
@@ -2793,7 +2797,7 @@
           <t>IRR less the sponsor hurdle (negative = below it)</t>
         </is>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="10">
         <f>'LBO'!$C$33-'Assumptions'!$C$65</f>
         <v/>
       </c>
@@ -2804,7 +2808,7 @@
           <t>Exit EV/EBITDA that would clear the hurdle (against the entry multiple above)</t>
         </is>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="5">
         <f>('LBO'!$C$10*(1+'Assumptions'!$C$65)^'LBO'!$C$31+'LBO'!$C$29)/'LBO'!$C$26</f>
         <v/>
       </c>
@@ -2815,7 +2819,7 @@
           <t>Change in total debt over the hold (exit less entry, £m; positive = debt GREW)</t>
         </is>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="4">
         <f>'LBO'!$C$29-'LBO'!$C$7</f>
         <v/>
       </c>
@@ -2826,7 +2830,7 @@
           <t>EBITDA growth over the hold</t>
         </is>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="10">
         <f>'LBO'!$C$26/'LBO'!$C$4-1</f>
         <v/>
       </c>
@@ -2881,22 +2885,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Span</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Central</t>
         </is>
@@ -2908,19 +2912,19 @@
           <t>DCF (Gordon) — WACC +/-100bp, perpetuity growth +/-50bp</t>
         </is>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="18">
         <f>MIN('Sensitivity'!D5:H5,'Sensitivity'!D6:H6,'Sensitivity'!D7:H7,'Sensitivity'!D8:H8,'Sensitivity'!D9:H9)</f>
         <v/>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="18">
         <f>MAX('Sensitivity'!D5:H5,'Sensitivity'!D6:H6,'Sensitivity'!D7:H7,'Sensitivity'!D8:H8,'Sensitivity'!D9:H9)</f>
         <v/>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="18">
         <f>D4-C4</f>
         <v/>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="18">
         <f>'DCF'!$C$65</f>
         <v/>
       </c>
@@ -2931,19 +2935,19 @@
           <t>Trading comps — peer minimum to peer maximum EV/EBITDA</t>
         </is>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="18">
         <f>'Comps'!$C$47</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <f>'Comps'!$C$49</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="18">
         <f>D5-C5</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="18">
         <f>'Comps'!$C$48</f>
         <v/>
       </c>
@@ -2954,19 +2958,19 @@
           <t>52-week traded range — the market's own answer</t>
         </is>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="18">
         <f>'Comps'!$C$50</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="18">
         <f>'Comps'!$C$51</f>
         <v/>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="18">
         <f>D6-C6</f>
         <v/>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="18">
         <f>'Comps'!$C$24</f>
         <v/>
       </c>
@@ -3034,7 +3038,7 @@
           <t>Balance sheet balances in every forecast year</t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <f>AND(ABS('BS'!F19)&lt;1e-06,ABS('BS'!G19)&lt;1e-06,ABS('BS'!H19)&lt;1e-06,ABS('BS'!I19)&lt;1e-06,ABS('BS'!J19)&lt;1e-06)</f>
         <v/>
       </c>
@@ -3045,7 +3049,7 @@
           <t>Closing cash agrees across all three constructions of it, every year</t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <f>AND(AND(ABS('CF'!F20-'BS'!F8)&lt;1e-06,ABS('CF'!F20-'Schedules'!F48)&lt;1e-06),AND(ABS('CF'!G20-'BS'!G8)&lt;1e-06,ABS('CF'!G20-'Schedules'!G48)&lt;1e-06),AND(ABS('CF'!H20-'BS'!H8)&lt;1e-06,ABS('CF'!H20-'Schedules'!H48)&lt;1e-06),AND(ABS('CF'!I20-'BS'!I8)&lt;1e-06,ABS('CF'!I20-'Schedules'!I48)&lt;1e-06),AND(ABS('CF'!J20-'BS'!J8)&lt;1e-06,ABS('CF'!J20-'Schedules'!J48)&lt;1e-06))</f>
         <v/>
       </c>
@@ -3056,7 +3060,7 @@
           <t>Closing borrowings never negative (no accidental cash-as-debt)</t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <f>AND('Schedules'!F47&gt;=0,'Schedules'!G47&gt;=0,'Schedules'!H47&gt;=0,'Schedules'!I47&gt;=0,'Schedules'!J47&gt;=0)</f>
         <v/>
       </c>
@@ -3067,7 +3071,7 @@
           <t>Cash never falls below the £50m minimum the revolver defends</t>
         </is>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <f>AND('CF'!F20&gt;=50.0-1e-06,'CF'!G20&gt;=50.0-1e-06,'CF'!H20&gt;=50.0-1e-06,'CF'!I20&gt;=50.0-1e-06,'CF'!J20&gt;=50.0-1e-06)</f>
         <v/>
       </c>
@@ -3078,7 +3082,7 @@
           <t>Perpetuity growth is below WACC (the Gordon formula is defined)</t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <f>'DCF'!$C$21&lt;'DCF'!$C$5</f>
         <v/>
       </c>
@@ -3089,7 +3093,7 @@
           <t>Terminal value is below 97% of enterprise value</t>
         </is>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <f>'DCF'!$C$60&lt;0.97</f>
         <v/>
       </c>
@@ -3100,7 +3104,7 @@
           <t>No forecast revenue growth outside +/-50%</t>
         </is>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <f>AND(ABS('IS'!G3/'IS'!F3-1)&lt;0.5,ABS('IS'!H3/'IS'!G3-1)&lt;0.5,ABS('IS'!I3/'IS'!H3-1)&lt;0.5,ABS('IS'!J3/'IS'!I3-1)&lt;0.5)</f>
         <v/>
       </c>
@@ -3111,7 +3115,7 @@
           <t>Peak borrowings are an assumed facility upsize, not a solvency problem: lease-inclusive net debt / EBITDA below 2.0x every year</t>
         </is>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
         <f>AND(('Schedules'!F47-'Schedules'!F48+'Schedules'!F31)/'IS'!F7&lt;2.0,('Schedules'!G47-'Schedules'!G48+'Schedules'!G31)/'IS'!G7&lt;2.0,('Schedules'!H47-'Schedules'!H48+'Schedules'!H31)/'IS'!H7&lt;2.0,('Schedules'!I47-'Schedules'!I48+'Schedules'!I31)/'IS'!I7&lt;2.0,('Schedules'!J47-'Schedules'!J48+'Schedules'!J31)/'IS'!J7&lt;2.0)</f>
         <v/>
       </c>
@@ -3129,7 +3133,7 @@
           <t>Peak forecast borrowings (£m) — against the £100m facility drawn at FY2025</t>
         </is>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="4">
         <f>MAX('Schedules'!F47,'Schedules'!G47,'Schedules'!H47,'Schedules'!I47,'Schedules'!J47)</f>
         <v/>
       </c>
@@ -3140,7 +3144,7 @@
           <t>Peak lease-inclusive net debt / EBITDA (x) — the basis the check uses</t>
         </is>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <f>MAX(('Schedules'!F47-'Schedules'!F48+'Schedules'!F31)/'IS'!F7,('Schedules'!G47-'Schedules'!G48+'Schedules'!G31)/'IS'!G7,('Schedules'!H47-'Schedules'!H48+'Schedules'!H31)/'IS'!H7,('Schedules'!I47-'Schedules'!I48+'Schedules'!I31)/'IS'!I7,('Schedules'!J47-'Schedules'!J48+'Schedules'!J31)/'IS'!J7)</f>
         <v/>
       </c>
@@ -3151,7 +3155,7 @@
           <t>Memo: peak gross borrowings / EBITDA (x) — the flattering basis, shown so the difference is visible rather than hidden</t>
         </is>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <f>MAX('Schedules'!F47/'IS'!F7,'Schedules'!G47/'IS'!G7,'Schedules'!H47/'IS'!H7,'Schedules'!I47/'IS'!I7,'Schedules'!J47/'IS'!J7)</f>
         <v/>
       </c>
@@ -3206,27 +3210,27 @@
       </c>
     </row>
     <row r="2">
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>FY2026</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>FY2027</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>FY2028</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>FY2029</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>FY2030</t>
         </is>
@@ -3238,7 +3242,7 @@
           <t>SCENARIO (Bear / Base / Bull)</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
@@ -3257,19 +3261,19 @@
           <t>Revenue growth — Bear</t>
         </is>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>0.025</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="8" t="n">
         <v>0.02</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="8" t="n">
         <v>0.015</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="J6" s="8" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -3279,19 +3283,19 @@
           <t>Revenue growth — Base</t>
         </is>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="8" t="n">
         <v>0.06</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="8" t="n">
         <v>0.055</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="J7" s="8" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -3301,19 +3305,19 @@
           <t>Revenue growth — Bull</t>
         </is>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <v>0.08499999999999999</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="8" t="n">
         <v>0.07500000000000001</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="J8" s="8" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -3323,19 +3327,19 @@
           <t>Gross margin — Bear</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="8" t="n">
         <v>0.5996</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="8" t="n">
         <v>0.6015</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="8" t="n">
         <v>0.603</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="8" t="n">
         <v>0.604</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="J9" s="8" t="n">
         <v>0.605</v>
       </c>
     </row>
@@ -3345,19 +3349,19 @@
           <t>Gross margin — Base</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="8" t="n">
         <v>0.6146</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="8" t="n">
         <v>0.6165</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="8" t="n">
         <v>0.618</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="8" t="n">
         <v>0.619</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="J10" s="8" t="n">
         <v>0.62</v>
       </c>
     </row>
@@ -3367,19 +3371,19 @@
           <t>Gross margin — Bull</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="8" t="n">
         <v>0.6296</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="8" t="n">
         <v>0.6315000000000001</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="8" t="n">
         <v>0.633</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="8" t="n">
         <v>0.634</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J11" s="8" t="n">
         <v>0.635</v>
       </c>
     </row>
@@ -3389,19 +3393,19 @@
           <t>Operating costs (% of revenue) — Bear</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="8" t="n">
         <v>0.4613</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="8" t="n">
         <v>0.458</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="8" t="n">
         <v>0.456</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="8" t="n">
         <v>0.4545</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="J12" s="8" t="n">
         <v>0.453</v>
       </c>
     </row>
@@ -3411,19 +3415,19 @@
           <t>Operating costs (% of revenue) — Base</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="8" t="n">
         <v>0.4513</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="8" t="n">
         <v>0.448</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="8" t="n">
         <v>0.446</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="8" t="n">
         <v>0.4445</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="J13" s="8" t="n">
         <v>0.443</v>
       </c>
     </row>
@@ -3433,19 +3437,19 @@
           <t>Operating costs (% of revenue) — Bull</t>
         </is>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="8" t="n">
         <v>0.4413</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="8" t="n">
         <v>0.438</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H14" s="8" t="n">
         <v>0.436</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="8" t="n">
         <v>0.4345</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="J14" s="8" t="n">
         <v>0.433</v>
       </c>
     </row>
@@ -3455,19 +3459,19 @@
           <t>Total capex (% of revenue) — Bear</t>
         </is>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="8" t="n">
         <v>0.1227</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="8" t="n">
         <v>0.111</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H15" s="8" t="n">
         <v>0.096</v>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I15" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="J15" s="7" t="n">
+      <c r="J15" s="8" t="n">
         <v>0.0682</v>
       </c>
     </row>
@@ -3477,19 +3481,19 @@
           <t>Total capex (% of revenue) — Base</t>
         </is>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="8" t="n">
         <v>0.1327</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="8" t="n">
         <v>0.121</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="H16" s="8" t="n">
         <v>0.106</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="8" t="n">
         <v>0.09</v>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="J16" s="8" t="n">
         <v>0.07770000000000001</v>
       </c>
     </row>
@@ -3499,19 +3503,19 @@
           <t>Total capex (% of revenue) — Bull</t>
         </is>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="8" t="n">
         <v>0.1407</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="8" t="n">
         <v>0.129</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="H17" s="8" t="n">
         <v>0.114</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="8" t="n">
         <v>0.098</v>
       </c>
-      <c r="J17" s="7" t="n">
+      <c r="J17" s="8" t="n">
         <v>0.0852</v>
       </c>
     </row>
@@ -3521,19 +3525,19 @@
           <t>ROU additions (% of revenue) — Bear</t>
         </is>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="8" t="n">
         <v>0.031</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="8" t="n">
         <v>0.0324</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="H18" s="8" t="n">
         <v>0.0338</v>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="I18" s="8" t="n">
         <v>0.0352</v>
       </c>
-      <c r="J18" s="7" t="n">
+      <c r="J18" s="8" t="n">
         <v>0.03659999999999999</v>
       </c>
     </row>
@@ -3543,19 +3547,19 @@
           <t>ROU additions (% of revenue) — Base</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="8" t="n">
         <v>0.0364</v>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="H19" s="8" t="n">
         <v>0.0378</v>
       </c>
-      <c r="I19" s="7" t="n">
+      <c r="I19" s="8" t="n">
         <v>0.0392</v>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="J19" s="8" t="n">
         <v>0.0406</v>
       </c>
     </row>
@@ -3565,19 +3569,19 @@
           <t>ROU additions (% of revenue) — Bull</t>
         </is>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="8" t="n">
         <v>0.03900000000000001</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="8" t="n">
         <v>0.04040000000000001</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H20" s="8" t="n">
         <v>0.0418</v>
       </c>
-      <c r="I20" s="7" t="n">
+      <c r="I20" s="8" t="n">
         <v>0.0432</v>
       </c>
-      <c r="J20" s="7" t="n">
+      <c r="J20" s="8" t="n">
         <v>0.0446</v>
       </c>
     </row>
@@ -3587,7 +3591,7 @@
           <t>Exit EV/EBITDA multiple — Bear</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="9" t="n">
         <v>5.07</v>
       </c>
     </row>
@@ -3597,7 +3601,7 @@
           <t>Exit EV/EBITDA multiple — Base</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="9" t="n">
         <v>6.31</v>
       </c>
     </row>
@@ -3607,7 +3611,7 @@
           <t>Exit EV/EBITDA multiple — Bull</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="9" t="n">
         <v>7.24</v>
       </c>
     </row>
@@ -3624,23 +3628,23 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!F6,'Assumptions'!F7,'Assumptions'!F8)</f>
         <v/>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!G6,'Assumptions'!G7,'Assumptions'!G8)</f>
         <v/>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!H6,'Assumptions'!H7,'Assumptions'!H8)</f>
         <v/>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!I6,'Assumptions'!I7,'Assumptions'!I8)</f>
         <v/>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!J6,'Assumptions'!J7,'Assumptions'!J8)</f>
         <v/>
       </c>
@@ -3651,23 +3655,23 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!F9,'Assumptions'!F10,'Assumptions'!F11)</f>
         <v/>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!G9,'Assumptions'!G10,'Assumptions'!G11)</f>
         <v/>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!H9,'Assumptions'!H10,'Assumptions'!H11)</f>
         <v/>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!I9,'Assumptions'!I10,'Assumptions'!I11)</f>
         <v/>
       </c>
-      <c r="J27" s="9">
+      <c r="J27" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!J9,'Assumptions'!J10,'Assumptions'!J11)</f>
         <v/>
       </c>
@@ -3678,23 +3682,23 @@
           <t>Operating costs (% of revenue)</t>
         </is>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!F12,'Assumptions'!F13,'Assumptions'!F14)</f>
         <v/>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!G12,'Assumptions'!G13,'Assumptions'!G14)</f>
         <v/>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!H12,'Assumptions'!H13,'Assumptions'!H14)</f>
         <v/>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!I12,'Assumptions'!I13,'Assumptions'!I14)</f>
         <v/>
       </c>
-      <c r="J28" s="9">
+      <c r="J28" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!J12,'Assumptions'!J13,'Assumptions'!J14)</f>
         <v/>
       </c>
@@ -3705,23 +3709,23 @@
           <t>Total capex (% of revenue)</t>
         </is>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!F15,'Assumptions'!F16,'Assumptions'!F17)</f>
         <v/>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!G15,'Assumptions'!G16,'Assumptions'!G17)</f>
         <v/>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!H15,'Assumptions'!H16,'Assumptions'!H17)</f>
         <v/>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!I15,'Assumptions'!I16,'Assumptions'!I17)</f>
         <v/>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!J15,'Assumptions'!J16,'Assumptions'!J17)</f>
         <v/>
       </c>
@@ -3732,23 +3736,23 @@
           <t>ROU additions (% of revenue)</t>
         </is>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!F18,'Assumptions'!F19,'Assumptions'!F20)</f>
         <v/>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!G18,'Assumptions'!G19,'Assumptions'!G20)</f>
         <v/>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!H18,'Assumptions'!H19,'Assumptions'!H20)</f>
         <v/>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!I18,'Assumptions'!I19,'Assumptions'!I20)</f>
         <v/>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="10">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!J18,'Assumptions'!J19,'Assumptions'!J20)</f>
         <v/>
       </c>
@@ -3759,7 +3763,7 @@
           <t>Exit EV/EBITDA multiple</t>
         </is>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="5">
         <f>CHOOSE(MATCH('Assumptions'!$C$3,{"Bear";"Base";"Bull"},0),'Assumptions'!C21,'Assumptions'!C22,'Assumptions'!C23)</f>
         <v/>
       </c>
@@ -3777,7 +3781,7 @@
           <t>Inventory days (on cost of sales)</t>
         </is>
       </c>
-      <c r="C34" s="10" t="n">
+      <c r="C34" s="11" t="n">
         <v>24.5</v>
       </c>
     </row>
@@ -3787,7 +3791,7 @@
           <t>Receivable days (on revenue)</t>
         </is>
       </c>
-      <c r="C35" s="10" t="n">
+      <c r="C35" s="11" t="n">
         <v>11.8</v>
       </c>
     </row>
@@ -3797,7 +3801,7 @@
           <t>Payable days (on cost of sales)</t>
         </is>
       </c>
-      <c r="C36" s="10" t="n">
+      <c r="C36" s="11" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3807,7 +3811,7 @@
           <t>PP&amp;E depreciation rate (of opening PP&amp;E)</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="8" t="n">
         <v>0.1423</v>
       </c>
     </row>
@@ -3817,7 +3821,7 @@
           <t>ROU depreciation rate (of opening ROU)</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="8" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -3827,7 +3831,7 @@
           <t>Corporation tax rate</t>
         </is>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="8" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -3837,7 +3841,7 @@
           <t>Dividend payout ratio (of net income)</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="8" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3847,7 +3851,7 @@
           <t>Minimum cash balance (£m)</t>
         </is>
       </c>
-      <c r="C41" s="11" t="n">
+      <c r="C41" s="12" t="n">
         <v>50</v>
       </c>
     </row>
@@ -3857,7 +3861,7 @@
           <t>Days in year (working capital basis)</t>
         </is>
       </c>
-      <c r="C42" s="10" t="n">
+      <c r="C42" s="11" t="n">
         <v>365</v>
       </c>
     </row>
@@ -3867,7 +3871,7 @@
           <t>RCF interest rate (risk-free + ~150bp, estimate)</t>
         </is>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="8" t="n">
         <v>0.055</v>
       </c>
     </row>
@@ -3877,7 +3881,7 @@
           <t>Revolver interest rate (charged in the debt schedule)</t>
         </is>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="10">
         <f>'Assumptions'!$C$43</f>
         <v/>
       </c>
@@ -3888,7 +3892,7 @@
           <t>Risk-free rate (UK 10-year gilt, estimate)</t>
         </is>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="8" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -3898,7 +3902,7 @@
           <t>Equity risk premium (UK, estimate)</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="8" t="n">
         <v>0.055</v>
       </c>
     </row>
@@ -3908,7 +3912,7 @@
           <t>Levered equity beta (estimate)</t>
         </is>
       </c>
-      <c r="C47" s="10" t="n">
+      <c r="C47" s="11" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -3918,7 +3922,7 @@
           <t>Debt weight in WACC (incl. leases)</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="8" t="n">
         <v>0.2075</v>
       </c>
     </row>
@@ -3928,7 +3932,7 @@
           <t>Perpetuity growth rate</t>
         </is>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="8" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -3945,7 +3949,7 @@
           <t>FY2025 interest on lease liabilities (FY2025 AR p.128)</t>
         </is>
       </c>
-      <c r="C52" s="11" t="n">
+      <c r="C52" s="12" t="n">
         <v>16.7</v>
       </c>
     </row>
@@ -3955,7 +3959,7 @@
           <t>IFRS 16 lease discount rate (= FY2025 lease interest / FY2024 liability)</t>
         </is>
       </c>
-      <c r="C53" s="9">
+      <c r="C53" s="10">
         <f>'Assumptions'!$C$52/'Historicals'!D30</f>
         <v/>
       </c>
@@ -3966,7 +3970,7 @@
           <t>Undiscounted lease cash flows, total (FY2025 AR p.154)</t>
         </is>
       </c>
-      <c r="C54" s="11" t="n">
+      <c r="C54" s="12" t="n">
         <v>582.3</v>
       </c>
     </row>
@@ -3976,7 +3980,7 @@
           <t>Undiscounted lease cash flows, &lt; 1 year (FY2025 AR p.154)</t>
         </is>
       </c>
-      <c r="C55" s="11" t="n">
+      <c r="C55" s="12" t="n">
         <v>79.09999999999999</v>
       </c>
     </row>
@@ -3986,7 +3990,7 @@
           <t>Implied average lease term, years (= total / &lt; 1 year)</t>
         </is>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="13">
         <f>'Assumptions'!$C$54/'Assumptions'!$C$55</f>
         <v/>
       </c>
@@ -3997,7 +4001,7 @@
           <t>Principal repaid on in-year lease additions (empirical fit)</t>
         </is>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="8" t="n">
         <v>0.0924</v>
       </c>
     </row>
@@ -4007,7 +4011,7 @@
           <t>Intangible share of total capex (FY2024-25 implied additions / capex)</t>
         </is>
       </c>
-      <c r="C58" s="9">
+      <c r="C58" s="10">
         <f>(('Historicals'!D22-'Historicals'!C22+'Historicals'!D8)+('Historicals'!E22-'Historicals'!D22+'Historicals'!E8))/('Historicals'!D38+'Historicals'!E38)</f>
         <v/>
       </c>
@@ -4018,7 +4022,7 @@
           <t>PP&amp;E share of total capex (= 1 - intangible share)</t>
         </is>
       </c>
-      <c r="C59" s="9">
+      <c r="C59" s="10">
         <f>1-'Assumptions'!$C$58</f>
         <v/>
       </c>
@@ -4029,7 +4033,7 @@
           <t>Amortisation rate (= FY2025 amortisation / FY2024 intangibles)</t>
         </is>
       </c>
-      <c r="C60" s="9">
+      <c r="C60" s="10">
         <f>'Historicals'!E8/'Historicals'!D22</f>
         <v/>
       </c>
@@ -4040,7 +4044,7 @@
           <t>Cost of debt for the WACC (RCF/lease blend, gross-weighted)</t>
         </is>
       </c>
-      <c r="C61" s="9">
+      <c r="C61" s="10">
         <f>('Historicals'!E31*'Assumptions'!$C$43+'Historicals'!E30*'Assumptions'!$C$53)/('Historicals'!E31+'Historicals'!E30)</f>
         <v/>
       </c>
@@ -4058,7 +4062,7 @@
           <t>Sponsor entry leverage (x EBITDA, total net debt INCLUDING leases)</t>
         </is>
       </c>
-      <c r="C64" s="8" t="n">
+      <c r="C64" s="9" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4068,7 +4072,7 @@
           <t>Sponsor IRR hurdle (conventional underwriting hurdle)</t>
         </is>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="8" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -4113,17 +4117,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -4135,13 +4139,13 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="12" t="n">
         <v>1809.6</v>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="12" t="n">
         <v>2014.4</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="12" t="n">
         <v>2151.2</v>
       </c>
       <c r="L3" t="inlineStr">
@@ -4156,13 +4160,13 @@
           <t>Cost of sales</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="12" t="n">
         <v>710.5</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="12" t="n">
         <v>770.8</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="12" t="n">
         <v>829.1</v>
       </c>
       <c r="L4" t="inlineStr">
@@ -4177,13 +4181,13 @@
           <t>Operating costs (excl. D&amp;A and impairment)</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <v>777.9</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>889.2</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="12" t="n">
         <v>970.9</v>
       </c>
       <c r="L5" t="inlineStr">
@@ -4198,13 +4202,13 @@
           <t>Depreciation of PP&amp;E (incl. net impairment)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>79.5</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="L6" t="inlineStr">
@@ -4219,13 +4223,13 @@
           <t>Depreciation of ROU assets (incl. net impairment)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>61.3</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>68.2</v>
       </c>
       <c r="L7" t="inlineStr">
@@ -4240,13 +4244,13 @@
           <t>Amortisation of intangibles</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>3.9</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>4.2</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>4.7</v>
       </c>
       <c r="L8" t="inlineStr">
@@ -4261,13 +4265,13 @@
           <t>Finance costs (incl. lease interest)</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>10.1</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>13.6</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="L9" t="inlineStr">
@@ -4282,13 +4286,13 @@
           <t>Finance income</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <v>6.1</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>8.1</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>1.8</v>
       </c>
       <c r="L10" t="inlineStr">
@@ -4303,13 +4307,13 @@
           <t>Tax expense</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="12" t="n">
         <v>45.8</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>50.5</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="12" t="n">
         <v>45.2</v>
       </c>
       <c r="L11" t="inlineStr">
@@ -4324,15 +4328,15 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="4">
         <f>'Historicals'!C3-'Historicals'!C4</f>
         <v/>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="4">
         <f>'Historicals'!D3-'Historicals'!D4</f>
         <v/>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="4">
         <f>'Historicals'!E3-'Historicals'!E4</f>
         <v/>
       </c>
@@ -4343,15 +4347,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="4">
         <f>'Historicals'!C12-'Historicals'!C5</f>
         <v/>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="4">
         <f>'Historicals'!D12-'Historicals'!D5</f>
         <v/>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="4">
         <f>'Historicals'!E12-'Historicals'!E5</f>
         <v/>
       </c>
@@ -4362,15 +4366,15 @@
           <t>Total D&amp;A (incl. impairment)</t>
         </is>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="4">
         <f>'Historicals'!C6+'Historicals'!C7+'Historicals'!C8</f>
         <v/>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="4">
         <f>'Historicals'!D6+'Historicals'!D7+'Historicals'!D8</f>
         <v/>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="4">
         <f>'Historicals'!E6+'Historicals'!E7+'Historicals'!E8</f>
         <v/>
       </c>
@@ -4381,15 +4385,15 @@
           <t>EBIT (operating profit)</t>
         </is>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="4">
         <f>'Historicals'!C13-'Historicals'!C14</f>
         <v/>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="4">
         <f>'Historicals'!D13-'Historicals'!D14</f>
         <v/>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="4">
         <f>'Historicals'!E13-'Historicals'!E14</f>
         <v/>
       </c>
@@ -4400,15 +4404,15 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="4">
         <f>'Historicals'!C15+'Historicals'!C10-'Historicals'!C9</f>
         <v/>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="4">
         <f>'Historicals'!D15+'Historicals'!D10-'Historicals'!D9</f>
         <v/>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="4">
         <f>'Historicals'!E15+'Historicals'!E10-'Historicals'!E9</f>
         <v/>
       </c>
@@ -4419,15 +4423,15 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="4">
         <f>'Historicals'!C16-'Historicals'!C11</f>
         <v/>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="4">
         <f>'Historicals'!D16-'Historicals'!D11</f>
         <v/>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="4">
         <f>'Historicals'!E16-'Historicals'!E11</f>
         <v/>
       </c>
@@ -4445,13 +4449,13 @@
           <t>Property, plant and equipment</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" s="12" t="n">
         <v>510.3</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="12" t="n">
         <v>664.7</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="12" t="n">
         <v>832.1</v>
       </c>
       <c r="L20" t="inlineStr">
@@ -4466,13 +4470,13 @@
           <t>Right-of-use assets</t>
         </is>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" s="12" t="n">
         <v>296.6</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="12" t="n">
         <v>387.2</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="12" t="n">
         <v>413</v>
       </c>
       <c r="L21" t="inlineStr">
@@ -4487,13 +4491,13 @@
           <t>Intangible assets</t>
         </is>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="C22" s="12" t="n">
         <v>18.3</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="12" t="n">
         <v>24.9</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="12" t="n">
         <v>43</v>
       </c>
       <c r="L22" t="inlineStr">
@@ -4508,13 +4512,13 @@
           <t>Inventories</t>
         </is>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C23" s="12" t="n">
         <v>48.8</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="12" t="n">
         <v>55.2</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" s="12" t="n">
         <v>55.7</v>
       </c>
       <c r="L23" t="inlineStr">
@@ -4529,13 +4533,13 @@
           <t>Trade and other receivables</t>
         </is>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C24" s="12" t="n">
         <v>53.8</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="12" t="n">
         <v>62.4</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="12" t="n">
         <v>69.40000000000001</v>
       </c>
       <c r="L24" t="inlineStr">
@@ -4550,13 +4554,13 @@
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="C25" s="12" t="n">
         <v>195.3</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="12" t="n">
         <v>125.3</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="12" t="n">
         <v>70.8</v>
       </c>
       <c r="L25" t="inlineStr">
@@ -4571,13 +4575,13 @@
           <t>Other assets</t>
         </is>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="C26" s="12" t="n">
         <v>6.6</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="inlineStr">
@@ -4592,15 +4596,15 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="4">
         <f>'Historicals'!C20+'Historicals'!C21+'Historicals'!C22+'Historicals'!C23+'Historicals'!C24+'Historicals'!C25+'Historicals'!C26</f>
         <v/>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="4">
         <f>'Historicals'!D20+'Historicals'!D21+'Historicals'!D22+'Historicals'!D23+'Historicals'!D24+'Historicals'!D25+'Historicals'!D26</f>
         <v/>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="4">
         <f>'Historicals'!E20+'Historicals'!E21+'Historicals'!E22+'Historicals'!E23+'Historicals'!E24+'Historicals'!E25+'Historicals'!E26</f>
         <v/>
       </c>
@@ -4611,13 +4615,13 @@
           <t>Trade and other payables</t>
         </is>
       </c>
-      <c r="C29" s="11" t="n">
+      <c r="C29" s="12" t="n">
         <v>211.1</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="12" t="n">
         <v>243.9</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E29" s="12" t="n">
         <v>272.8</v>
       </c>
       <c r="L29" t="inlineStr">
@@ -4632,13 +4636,13 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C30" s="12" t="n">
         <v>319.6</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="12" t="n">
         <v>415.1</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" s="12" t="n">
         <v>449.8</v>
       </c>
       <c r="L30" t="inlineStr">
@@ -4653,13 +4657,13 @@
           <t>Borrowings (RCF drawn)</t>
         </is>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="C31" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L31" t="inlineStr">
@@ -4674,13 +4678,13 @@
           <t>Other liabilities</t>
         </is>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="C32" s="12" t="n">
         <v>68.09999999999999</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="12" t="n">
         <v>90.2</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="E32" s="12" t="n">
         <v>111.2</v>
       </c>
       <c r="L32" t="inlineStr">
@@ -4695,13 +4699,13 @@
           <t>Total equity</t>
         </is>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="C33" s="12" t="n">
         <v>530.9</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="12" t="n">
         <v>570.5</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="12" t="n">
         <v>625.2</v>
       </c>
       <c r="L33" t="inlineStr">
@@ -4716,15 +4720,15 @@
           <t>Total liabilities and equity</t>
         </is>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="4">
         <f>'Historicals'!C29+'Historicals'!C30+'Historicals'!C31+'Historicals'!C32+'Historicals'!C33</f>
         <v/>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="4">
         <f>'Historicals'!D29+'Historicals'!D30+'Historicals'!D31+'Historicals'!D32+'Historicals'!D33</f>
         <v/>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="4">
         <f>'Historicals'!E29+'Historicals'!E30+'Historicals'!E31+'Historicals'!E32+'Historicals'!E33</f>
         <v/>
       </c>
@@ -4735,15 +4739,15 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="4">
         <f>'Historicals'!C23+'Historicals'!C24-'Historicals'!C29</f>
         <v/>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="4">
         <f>'Historicals'!D23+'Historicals'!D24-'Historicals'!D29</f>
         <v/>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="4">
         <f>'Historicals'!E23+'Historicals'!E24-'Historicals'!E29</f>
         <v/>
       </c>
@@ -4761,13 +4765,13 @@
           <t>Capital expenditure (total cash, PP&amp;E + intangibles)</t>
         </is>
       </c>
-      <c r="C38" s="11" t="n">
+      <c r="C38" s="12" t="n">
         <v>198.1</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D38" s="12" t="n">
         <v>240.9</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="12" t="n">
         <v>285.4</v>
       </c>
       <c r="L38" t="inlineStr">
@@ -4782,13 +4786,13 @@
           <t>Repayment of lease principal</t>
         </is>
       </c>
-      <c r="C39" s="11" t="n">
+      <c r="C39" s="12" t="n">
         <v>53.7</v>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D39" s="12" t="n">
         <v>56.7</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E39" s="12" t="n">
         <v>63.3</v>
       </c>
       <c r="L39" t="inlineStr">
@@ -4803,13 +4807,13 @@
           <t>New right-of-use asset additions</t>
         </is>
       </c>
-      <c r="C40" s="11" t="n">
+      <c r="C40" s="12" t="n">
         <v>70.3</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="12" t="n">
         <v>143.8</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="12" t="n">
         <v>74.8</v>
       </c>
       <c r="L40" t="inlineStr">
@@ -4824,13 +4828,13 @@
           <t>Dividends paid</t>
         </is>
       </c>
-      <c r="C41" s="11" t="n">
+      <c r="C41" s="12" t="n">
         <v>60.8</v>
       </c>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="12" t="n">
         <v>106.8</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="12" t="n">
         <v>70.3</v>
       </c>
       <c r="L41" t="inlineStr">
@@ -4852,7 +4856,7 @@
           <t>Weighted average shares in issue, diluted (m)</t>
         </is>
       </c>
-      <c r="E44" s="10" t="n">
+      <c r="E44" s="11" t="n">
         <v>102.482895</v>
       </c>
       <c r="L44" t="inlineStr">
@@ -4897,23 +4901,23 @@
       </c>
     </row>
     <row r="2">
-      <c r="F2" s="5">
+      <c r="F2" s="6">
         <f>'Assumptions'!F$2</f>
         <v/>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <f>'Assumptions'!G$2</f>
         <v/>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="6">
         <f>'Assumptions'!H$2</f>
         <v/>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="6">
         <f>'Assumptions'!I$2</f>
         <v/>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="6">
         <f>'Assumptions'!J$2</f>
         <v/>
       </c>
@@ -4924,23 +4928,23 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="4">
         <f>'Historicals'!E3*(1+'Assumptions'!F26)</f>
         <v/>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="4">
         <f>'IS'!F3*(1+'Assumptions'!G26)</f>
         <v/>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="4">
         <f>'IS'!G3*(1+'Assumptions'!H26)</f>
         <v/>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="4">
         <f>'IS'!H3*(1+'Assumptions'!I26)</f>
         <v/>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="4">
         <f>'IS'!I3*(1+'Assumptions'!J26)</f>
         <v/>
       </c>
@@ -4951,23 +4955,23 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="4">
         <f>'IS'!F3*'Assumptions'!F27</f>
         <v/>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="4">
         <f>'IS'!G3*'Assumptions'!G27</f>
         <v/>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="4">
         <f>'IS'!H3*'Assumptions'!H27</f>
         <v/>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="4">
         <f>'IS'!I3*'Assumptions'!I27</f>
         <v/>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="4">
         <f>'IS'!J3*'Assumptions'!J27</f>
         <v/>
       </c>
@@ -4978,23 +4982,23 @@
           <t>Cost of sales (memo: revenue less gross profit)</t>
         </is>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <f>'IS'!F3-'IS'!F4</f>
         <v/>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="4">
         <f>'IS'!G3-'IS'!G4</f>
         <v/>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="4">
         <f>'IS'!H3-'IS'!H4</f>
         <v/>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="4">
         <f>'IS'!I3-'IS'!I4</f>
         <v/>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="4">
         <f>'IS'!J3-'IS'!J4</f>
         <v/>
       </c>
@@ -5005,23 +5009,23 @@
           <t>Operating costs (excl. D&amp;A)</t>
         </is>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <f>'IS'!F3*'Assumptions'!F28</f>
         <v/>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="4">
         <f>'IS'!G3*'Assumptions'!G28</f>
         <v/>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="4">
         <f>'IS'!H3*'Assumptions'!H28</f>
         <v/>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="4">
         <f>'IS'!I3*'Assumptions'!I28</f>
         <v/>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="4">
         <f>'IS'!J3*'Assumptions'!J28</f>
         <v/>
       </c>
@@ -5032,23 +5036,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <f>'IS'!F4-'IS'!F6</f>
         <v/>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="4">
         <f>'IS'!G4-'IS'!G6</f>
         <v/>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="4">
         <f>'IS'!H4-'IS'!H6</f>
         <v/>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="4">
         <f>'IS'!I4-'IS'!I6</f>
         <v/>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="4">
         <f>'IS'!J4-'IS'!J6</f>
         <v/>
       </c>
@@ -5059,23 +5063,23 @@
           <t>Depreciation of PP&amp;E</t>
         </is>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <f>'Schedules'!F13</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="14">
         <f>'Schedules'!G13</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <f>'Schedules'!H13</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="14">
         <f>'Schedules'!I13</f>
         <v/>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="14">
         <f>'Schedules'!J13</f>
         <v/>
       </c>
@@ -5086,23 +5090,23 @@
           <t>Depreciation of ROU assets</t>
         </is>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <f>'Schedules'!F26</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="14">
         <f>'Schedules'!G26</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="14">
         <f>'Schedules'!H26</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="14">
         <f>'Schedules'!I26</f>
         <v/>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="14">
         <f>'Schedules'!J26</f>
         <v/>
       </c>
@@ -5113,23 +5117,23 @@
           <t>Amortisation</t>
         </is>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="14">
         <f>'Schedules'!F19</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="14">
         <f>'Schedules'!G19</f>
         <v/>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="14">
         <f>'Schedules'!H19</f>
         <v/>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="14">
         <f>'Schedules'!I19</f>
         <v/>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="14">
         <f>'Schedules'!J19</f>
         <v/>
       </c>
@@ -5140,23 +5144,23 @@
           <t>Total depreciation and amortisation</t>
         </is>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="4">
         <f>'IS'!F8+'IS'!F9+'IS'!F10</f>
         <v/>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="4">
         <f>'IS'!G8+'IS'!G9+'IS'!G10</f>
         <v/>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="4">
         <f>'IS'!H8+'IS'!H9+'IS'!H10</f>
         <v/>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="4">
         <f>'IS'!I8+'IS'!I9+'IS'!I10</f>
         <v/>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="4">
         <f>'IS'!J8+'IS'!J9+'IS'!J10</f>
         <v/>
       </c>
@@ -5167,23 +5171,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="4">
         <f>'IS'!F7-'IS'!F11</f>
         <v/>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="4">
         <f>'IS'!G7-'IS'!G11</f>
         <v/>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="4">
         <f>'IS'!H7-'IS'!H11</f>
         <v/>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="4">
         <f>'IS'!I7-'IS'!I11</f>
         <v/>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="4">
         <f>'IS'!J7-'IS'!J11</f>
         <v/>
       </c>
@@ -5194,23 +5198,23 @@
           <t>Lease interest</t>
         </is>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <f>'Schedules'!F29</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="14">
         <f>'Schedules'!G29</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="14">
         <f>'Schedules'!H29</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="14">
         <f>'Schedules'!I29</f>
         <v/>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="14">
         <f>'Schedules'!J29</f>
         <v/>
       </c>
@@ -5221,23 +5225,23 @@
           <t>Interest on borrowings</t>
         </is>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <f>'Schedules'!F43</f>
         <v/>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="14">
         <f>'Schedules'!G43</f>
         <v/>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="14">
         <f>'Schedules'!H43</f>
         <v/>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="14">
         <f>'Schedules'!I43</f>
         <v/>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="14">
         <f>'Schedules'!J43</f>
         <v/>
       </c>
@@ -5248,23 +5252,23 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="4">
         <f>'IS'!F12-'IS'!F13-'IS'!F14</f>
         <v/>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="4">
         <f>'IS'!G12-'IS'!G13-'IS'!G14</f>
         <v/>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="4">
         <f>'IS'!H12-'IS'!H13-'IS'!H14</f>
         <v/>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="4">
         <f>'IS'!I12-'IS'!I13-'IS'!I14</f>
         <v/>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="4">
         <f>'IS'!J12-'IS'!J13-'IS'!J14</f>
         <v/>
       </c>
@@ -5275,23 +5279,23 @@
           <t>Tax charge (nil in a loss year)</t>
         </is>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="4">
         <f>MAX('IS'!F15,0)*'Assumptions'!$C$39</f>
         <v/>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="4">
         <f>MAX('IS'!G15,0)*'Assumptions'!$C$39</f>
         <v/>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="4">
         <f>MAX('IS'!H15,0)*'Assumptions'!$C$39</f>
         <v/>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="4">
         <f>MAX('IS'!I15,0)*'Assumptions'!$C$39</f>
         <v/>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="4">
         <f>MAX('IS'!J15,0)*'Assumptions'!$C$39</f>
         <v/>
       </c>
@@ -5302,23 +5306,23 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="4">
         <f>'IS'!F15-'IS'!F16</f>
         <v/>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="4">
         <f>'IS'!G15-'IS'!G16</f>
         <v/>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="4">
         <f>'IS'!H15-'IS'!H16</f>
         <v/>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="4">
         <f>'IS'!I15-'IS'!I16</f>
         <v/>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="4">
         <f>'IS'!J15-'IS'!J16</f>
         <v/>
       </c>
@@ -5359,23 +5363,23 @@
       </c>
     </row>
     <row r="2">
-      <c r="F2" s="5">
+      <c r="F2" s="6">
         <f>'Assumptions'!F$2</f>
         <v/>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <f>'Assumptions'!G$2</f>
         <v/>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="6">
         <f>'Assumptions'!H$2</f>
         <v/>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="6">
         <f>'Assumptions'!I$2</f>
         <v/>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="6">
         <f>'Assumptions'!J$2</f>
         <v/>
       </c>
@@ -5386,23 +5390,23 @@
           <t>Property, plant and equipment</t>
         </is>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="14">
         <f>'Schedules'!F14</f>
         <v/>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="14">
         <f>'Schedules'!G14</f>
         <v/>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="14">
         <f>'Schedules'!H14</f>
         <v/>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="14">
         <f>'Schedules'!I14</f>
         <v/>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="14">
         <f>'Schedules'!J14</f>
         <v/>
       </c>
@@ -5413,23 +5417,23 @@
           <t>Right-of-use assets</t>
         </is>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="14">
         <f>'Schedules'!F27</f>
         <v/>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="14">
         <f>'Schedules'!G27</f>
         <v/>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="14">
         <f>'Schedules'!H27</f>
         <v/>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="14">
         <f>'Schedules'!I27</f>
         <v/>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="14">
         <f>'Schedules'!J27</f>
         <v/>
       </c>
@@ -5440,23 +5444,23 @@
           <t>Intangible assets</t>
         </is>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="14">
         <f>'Schedules'!F20</f>
         <v/>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="14">
         <f>'Schedules'!G20</f>
         <v/>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="14">
         <f>'Schedules'!H20</f>
         <v/>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="14">
         <f>'Schedules'!I20</f>
         <v/>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="14">
         <f>'Schedules'!J20</f>
         <v/>
       </c>
@@ -5467,23 +5471,23 @@
           <t>Inventories</t>
         </is>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <f>'Schedules'!F3</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="14">
         <f>'Schedules'!G3</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="14">
         <f>'Schedules'!H3</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="14">
         <f>'Schedules'!I3</f>
         <v/>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="14">
         <f>'Schedules'!J3</f>
         <v/>
       </c>
@@ -5494,23 +5498,23 @@
           <t>Trade and other receivables</t>
         </is>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="14">
         <f>'Schedules'!F4</f>
         <v/>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="14">
         <f>'Schedules'!G4</f>
         <v/>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="14">
         <f>'Schedules'!H4</f>
         <v/>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="14">
         <f>'Schedules'!I4</f>
         <v/>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="14">
         <f>'Schedules'!J4</f>
         <v/>
       </c>
@@ -5521,23 +5525,23 @@
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <f>'CF'!F20</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="14">
         <f>'CF'!G20</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <f>'CF'!H20</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="14">
         <f>'CF'!I20</f>
         <v/>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="14">
         <f>'CF'!J20</f>
         <v/>
       </c>
@@ -5548,23 +5552,23 @@
           <t>Other assets (held flat)</t>
         </is>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <f>'Historicals'!E26</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="14">
         <f>'Historicals'!E26</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="14">
         <f>'Historicals'!E26</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="14">
         <f>'Historicals'!E26</f>
         <v/>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="14">
         <f>'Historicals'!E26</f>
         <v/>
       </c>
@@ -5575,23 +5579,23 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="4">
         <f>'BS'!F3+'BS'!F4+'BS'!F5+'BS'!F6+'BS'!F7+'BS'!F8+'BS'!F9</f>
         <v/>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="4">
         <f>'BS'!G3+'BS'!G4+'BS'!G5+'BS'!G6+'BS'!G7+'BS'!G8+'BS'!G9</f>
         <v/>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="4">
         <f>'BS'!H3+'BS'!H4+'BS'!H5+'BS'!H6+'BS'!H7+'BS'!H8+'BS'!H9</f>
         <v/>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="4">
         <f>'BS'!I3+'BS'!I4+'BS'!I5+'BS'!I6+'BS'!I7+'BS'!I8+'BS'!I9</f>
         <v/>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="4">
         <f>'BS'!J3+'BS'!J4+'BS'!J5+'BS'!J6+'BS'!J7+'BS'!J8+'BS'!J9</f>
         <v/>
       </c>
@@ -5609,23 +5613,23 @@
           <t>Trade and other payables</t>
         </is>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <f>'Schedules'!F5</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="14">
         <f>'Schedules'!G5</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="14">
         <f>'Schedules'!H5</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="14">
         <f>'Schedules'!I5</f>
         <v/>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="14">
         <f>'Schedules'!J5</f>
         <v/>
       </c>
@@ -5636,23 +5640,23 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <f>'Schedules'!F31</f>
         <v/>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="14">
         <f>'Schedules'!G31</f>
         <v/>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="14">
         <f>'Schedules'!H31</f>
         <v/>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="14">
         <f>'Schedules'!I31</f>
         <v/>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="14">
         <f>'Schedules'!J31</f>
         <v/>
       </c>
@@ -5663,23 +5667,23 @@
           <t>Borrowings</t>
         </is>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <f>'Schedules'!F47</f>
         <v/>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="14">
         <f>'Schedules'!G47</f>
         <v/>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="14">
         <f>'Schedules'!H47</f>
         <v/>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="14">
         <f>'Schedules'!I47</f>
         <v/>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="14">
         <f>'Schedules'!J47</f>
         <v/>
       </c>
@@ -5690,23 +5694,23 @@
           <t>Other liabilities (held flat)</t>
         </is>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="14">
         <f>'Historicals'!E32</f>
         <v/>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="14">
         <f>'Historicals'!E32</f>
         <v/>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="14">
         <f>'Historicals'!E32</f>
         <v/>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="14">
         <f>'Historicals'!E32</f>
         <v/>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="14">
         <f>'Historicals'!E32</f>
         <v/>
       </c>
@@ -5717,23 +5721,23 @@
           <t>Total equity</t>
         </is>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="14">
         <f>'Schedules'!F36</f>
         <v/>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="14">
         <f>'Schedules'!G36</f>
         <v/>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="14">
         <f>'Schedules'!H36</f>
         <v/>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="14">
         <f>'Schedules'!I36</f>
         <v/>
       </c>
-      <c r="J17" s="13">
+      <c r="J17" s="14">
         <f>'Schedules'!J36</f>
         <v/>
       </c>
@@ -5744,23 +5748,23 @@
           <t>Total liabilities and equity</t>
         </is>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="4">
         <f>'BS'!F13+'BS'!F14+'BS'!F15+'BS'!F16+'BS'!F17</f>
         <v/>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="4">
         <f>'BS'!G13+'BS'!G14+'BS'!G15+'BS'!G16+'BS'!G17</f>
         <v/>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="4">
         <f>'BS'!H13+'BS'!H14+'BS'!H15+'BS'!H16+'BS'!H17</f>
         <v/>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="4">
         <f>'BS'!I13+'BS'!I14+'BS'!I15+'BS'!I16+'BS'!I17</f>
         <v/>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="4">
         <f>'BS'!J13+'BS'!J14+'BS'!J15+'BS'!J16+'BS'!J17</f>
         <v/>
       </c>
@@ -5771,23 +5775,23 @@
           <t>Balance check (total assets less total claims — must be nil)</t>
         </is>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="4">
         <f>'BS'!F10-'BS'!F18</f>
         <v/>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="4">
         <f>'BS'!G10-'BS'!G18</f>
         <v/>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="4">
         <f>'BS'!H10-'BS'!H18</f>
         <v/>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="4">
         <f>'BS'!I10-'BS'!I18</f>
         <v/>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="4">
         <f>'BS'!J10-'BS'!J18</f>
         <v/>
       </c>
@@ -5828,23 +5832,23 @@
       </c>
     </row>
     <row r="2">
-      <c r="F2" s="5">
+      <c r="F2" s="6">
         <f>'Assumptions'!F$2</f>
         <v/>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <f>'Assumptions'!G$2</f>
         <v/>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="6">
         <f>'Assumptions'!H$2</f>
         <v/>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="6">
         <f>'Assumptions'!I$2</f>
         <v/>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="6">
         <f>'Assumptions'!J$2</f>
         <v/>
       </c>
@@ -5855,23 +5859,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="14">
         <f>'IS'!F7</f>
         <v/>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="14">
         <f>'IS'!G7</f>
         <v/>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="14">
         <f>'IS'!H7</f>
         <v/>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="14">
         <f>'IS'!I7</f>
         <v/>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="14">
         <f>'IS'!J7</f>
         <v/>
       </c>
@@ -5882,23 +5886,23 @@
           <t>Increase in working capital (outflow when positive)</t>
         </is>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="14">
         <f>'Schedules'!F8</f>
         <v/>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="14">
         <f>'Schedules'!G8</f>
         <v/>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="14">
         <f>'Schedules'!H8</f>
         <v/>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="14">
         <f>'Schedules'!I8</f>
         <v/>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="14">
         <f>'Schedules'!J8</f>
         <v/>
       </c>
@@ -5909,23 +5913,23 @@
           <t>Tax paid</t>
         </is>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="14">
         <f>'IS'!F16</f>
         <v/>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="14">
         <f>'IS'!G16</f>
         <v/>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="14">
         <f>'IS'!H16</f>
         <v/>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="14">
         <f>'IS'!I16</f>
         <v/>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="14">
         <f>'IS'!J16</f>
         <v/>
       </c>
@@ -5936,23 +5940,23 @@
           <t>Cash from operations</t>
         </is>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <f>'CF'!F3-'CF'!F4-'CF'!F5</f>
         <v/>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="4">
         <f>'CF'!G3-'CF'!G4-'CF'!G5</f>
         <v/>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="4">
         <f>'CF'!H3-'CF'!H4-'CF'!H5</f>
         <v/>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="4">
         <f>'CF'!I3-'CF'!I4-'CF'!I5</f>
         <v/>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="4">
         <f>'CF'!J3-'CF'!J4-'CF'!J5</f>
         <v/>
       </c>
@@ -5970,23 +5974,23 @@
           <t>Capital expenditure (total)</t>
         </is>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <f>'Schedules'!F21</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="14">
         <f>'Schedules'!G21</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="14">
         <f>'Schedules'!H21</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="14">
         <f>'Schedules'!I21</f>
         <v/>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="14">
         <f>'Schedules'!J21</f>
         <v/>
       </c>
@@ -5997,23 +6001,23 @@
           <t xml:space="preserve">  of which PP&amp;E (memo)</t>
         </is>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="14">
         <f>'Schedules'!F12</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="14">
         <f>'Schedules'!G12</f>
         <v/>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="14">
         <f>'Schedules'!H12</f>
         <v/>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="14">
         <f>'Schedules'!I12</f>
         <v/>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="14">
         <f>'Schedules'!J12</f>
         <v/>
       </c>
@@ -6024,23 +6028,23 @@
           <t xml:space="preserve">  of which intangible (memo)</t>
         </is>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <f>'Schedules'!F18</f>
         <v/>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="14">
         <f>'Schedules'!G18</f>
         <v/>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="14">
         <f>'Schedules'!H18</f>
         <v/>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="14">
         <f>'Schedules'!I18</f>
         <v/>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="14">
         <f>'Schedules'!J18</f>
         <v/>
       </c>
@@ -6051,23 +6055,23 @@
           <t>Lease interest paid</t>
         </is>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <f>'Schedules'!F29</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="14">
         <f>'Schedules'!G29</f>
         <v/>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="14">
         <f>'Schedules'!H29</f>
         <v/>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="14">
         <f>'Schedules'!I29</f>
         <v/>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="14">
         <f>'Schedules'!J29</f>
         <v/>
       </c>
@@ -6078,23 +6082,23 @@
           <t>Lease principal repaid</t>
         </is>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <f>'Schedules'!F30</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="14">
         <f>'Schedules'!G30</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="14">
         <f>'Schedules'!H30</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="14">
         <f>'Schedules'!I30</f>
         <v/>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="14">
         <f>'Schedules'!J30</f>
         <v/>
       </c>
@@ -6105,23 +6109,23 @@
           <t>Interest paid on borrowings</t>
         </is>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <f>'Schedules'!F43</f>
         <v/>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="14">
         <f>'Schedules'!G43</f>
         <v/>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="14">
         <f>'Schedules'!H43</f>
         <v/>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="14">
         <f>'Schedules'!I43</f>
         <v/>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="14">
         <f>'Schedules'!J43</f>
         <v/>
       </c>
@@ -6132,23 +6136,23 @@
           <t>Repayment of borrowings</t>
         </is>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <f>'Schedules'!F45</f>
         <v/>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="14">
         <f>'Schedules'!G45</f>
         <v/>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="14">
         <f>'Schedules'!H45</f>
         <v/>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="14">
         <f>'Schedules'!I45</f>
         <v/>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="14">
         <f>'Schedules'!J45</f>
         <v/>
       </c>
@@ -6159,23 +6163,23 @@
           <t>Revolver draw (inflow)</t>
         </is>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="14">
         <f>'Schedules'!F46</f>
         <v/>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="14">
         <f>'Schedules'!G46</f>
         <v/>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="14">
         <f>'Schedules'!H46</f>
         <v/>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="14">
         <f>'Schedules'!I46</f>
         <v/>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="14">
         <f>'Schedules'!J46</f>
         <v/>
       </c>
@@ -6186,23 +6190,23 @@
           <t>Dividends paid</t>
         </is>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="14">
         <f>'Schedules'!F34</f>
         <v/>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="14">
         <f>'Schedules'!G34</f>
         <v/>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="14">
         <f>'Schedules'!H34</f>
         <v/>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="14">
         <f>'Schedules'!I34</f>
         <v/>
       </c>
-      <c r="J17" s="13">
+      <c r="J17" s="14">
         <f>'Schedules'!J34</f>
         <v/>
       </c>
@@ -6213,23 +6217,23 @@
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="4">
         <f>'CF'!F6-'CF'!F9-'CF'!F12-'CF'!F13-'CF'!F14-'CF'!F15+'CF'!F16-'CF'!F17</f>
         <v/>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="4">
         <f>'CF'!G6-'CF'!G9-'CF'!G12-'CF'!G13-'CF'!G14-'CF'!G15+'CF'!G16-'CF'!G17</f>
         <v/>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="4">
         <f>'CF'!H6-'CF'!H9-'CF'!H12-'CF'!H13-'CF'!H14-'CF'!H15+'CF'!H16-'CF'!H17</f>
         <v/>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="4">
         <f>'CF'!I6-'CF'!I9-'CF'!I12-'CF'!I13-'CF'!I14-'CF'!I15+'CF'!I16-'CF'!I17</f>
         <v/>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="4">
         <f>'CF'!J6-'CF'!J9-'CF'!J12-'CF'!J13-'CF'!J14-'CF'!J15+'CF'!J16-'CF'!J17</f>
         <v/>
       </c>
@@ -6240,23 +6244,23 @@
           <t>Opening cash</t>
         </is>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="4">
         <f>'Historicals'!E25</f>
         <v/>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="4">
         <f>'CF'!F20</f>
         <v/>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="4">
         <f>'CF'!G20</f>
         <v/>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="4">
         <f>'CF'!H20</f>
         <v/>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="4">
         <f>'CF'!I20</f>
         <v/>
       </c>
@@ -6267,23 +6271,23 @@
           <t>Closing cash</t>
         </is>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="4">
         <f>'CF'!F19+'CF'!F18</f>
         <v/>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="4">
         <f>'CF'!G19+'CF'!G18</f>
         <v/>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="4">
         <f>'CF'!H19+'CF'!H18</f>
         <v/>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="4">
         <f>'CF'!I19+'CF'!I18</f>
         <v/>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="4">
         <f>'CF'!J19+'CF'!J18</f>
         <v/>
       </c>
@@ -6324,23 +6328,23 @@
       </c>
     </row>
     <row r="2">
-      <c r="F2" s="5">
+      <c r="F2" s="6">
         <f>'Assumptions'!F$2</f>
         <v/>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <f>'Assumptions'!G$2</f>
         <v/>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="6">
         <f>'Assumptions'!H$2</f>
         <v/>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="6">
         <f>'Assumptions'!I$2</f>
         <v/>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="6">
         <f>'Assumptions'!J$2</f>
         <v/>
       </c>
@@ -6351,23 +6355,23 @@
           <t>Inventories (cost of sales x inventory days / 365)</t>
         </is>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="4">
         <f>'IS'!F5*'Assumptions'!$C$34/'Assumptions'!$C$42</f>
         <v/>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="4">
         <f>'IS'!G5*'Assumptions'!$C$34/'Assumptions'!$C$42</f>
         <v/>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="4">
         <f>'IS'!H5*'Assumptions'!$C$34/'Assumptions'!$C$42</f>
         <v/>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="4">
         <f>'IS'!I5*'Assumptions'!$C$34/'Assumptions'!$C$42</f>
         <v/>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="4">
         <f>'IS'!J5*'Assumptions'!$C$34/'Assumptions'!$C$42</f>
         <v/>
       </c>
@@ -6378,23 +6382,23 @@
           <t>Trade receivables (revenue x receivable days / 365)</t>
         </is>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="4">
         <f>'IS'!F3*'Assumptions'!$C$35/'Assumptions'!$C$42</f>
         <v/>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="4">
         <f>'IS'!G3*'Assumptions'!$C$35/'Assumptions'!$C$42</f>
         <v/>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="4">
         <f>'IS'!H3*'Assumptions'!$C$35/'Assumptions'!$C$42</f>
         <v/>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="4">
         <f>'IS'!I3*'Assumptions'!$C$35/'Assumptions'!$C$42</f>
         <v/>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="4">
         <f>'IS'!J3*'Assumptions'!$C$35/'Assumptions'!$C$42</f>
         <v/>
       </c>
@@ -6405,23 +6409,23 @@
           <t>Trade payables (cost of sales x payable days / 365)</t>
         </is>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <f>'IS'!F5*'Assumptions'!$C$36/'Assumptions'!$C$42</f>
         <v/>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="4">
         <f>'IS'!G5*'Assumptions'!$C$36/'Assumptions'!$C$42</f>
         <v/>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="4">
         <f>'IS'!H5*'Assumptions'!$C$36/'Assumptions'!$C$42</f>
         <v/>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="4">
         <f>'IS'!I5*'Assumptions'!$C$36/'Assumptions'!$C$42</f>
         <v/>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="4">
         <f>'IS'!J5*'Assumptions'!$C$36/'Assumptions'!$C$42</f>
         <v/>
       </c>
@@ -6432,23 +6436,23 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <f>'Schedules'!F3+'Schedules'!F4-'Schedules'!F5</f>
         <v/>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="4">
         <f>'Schedules'!G3+'Schedules'!G4-'Schedules'!G5</f>
         <v/>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="4">
         <f>'Schedules'!H3+'Schedules'!H4-'Schedules'!H5</f>
         <v/>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="4">
         <f>'Schedules'!I3+'Schedules'!I4-'Schedules'!I5</f>
         <v/>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="4">
         <f>'Schedules'!J3+'Schedules'!J4-'Schedules'!J5</f>
         <v/>
       </c>
@@ -6459,23 +6463,23 @@
           <t>Opening net working capital</t>
         </is>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <f>'Historicals'!E35</f>
         <v/>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="4">
         <f>'Schedules'!F6</f>
         <v/>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="4">
         <f>'Schedules'!G6</f>
         <v/>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="4">
         <f>'Schedules'!H6</f>
         <v/>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="4">
         <f>'Schedules'!I6</f>
         <v/>
       </c>
@@ -6486,23 +6490,23 @@
           <t>Increase in net working capital (cash outflow when positive)</t>
         </is>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="4">
         <f>'Schedules'!F6-'Schedules'!F7</f>
         <v/>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="4">
         <f>'Schedules'!G6-'Schedules'!G7</f>
         <v/>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="4">
         <f>'Schedules'!H6-'Schedules'!H7</f>
         <v/>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="4">
         <f>'Schedules'!I6-'Schedules'!I7</f>
         <v/>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="4">
         <f>'Schedules'!J6-'Schedules'!J7</f>
         <v/>
       </c>
@@ -6520,23 +6524,23 @@
           <t>Opening PP&amp;E</t>
         </is>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="4">
         <f>'Historicals'!E20</f>
         <v/>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="4">
         <f>'Schedules'!F14</f>
         <v/>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="4">
         <f>'Schedules'!G14</f>
         <v/>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="4">
         <f>'Schedules'!H14</f>
         <v/>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="4">
         <f>'Schedules'!I14</f>
         <v/>
       </c>
@@ -6547,23 +6551,23 @@
           <t>PP&amp;E capex (revenue x total capex % x PP&amp;E share)</t>
         </is>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="4">
         <f>'IS'!F3*'Assumptions'!F29*'Assumptions'!$C$59</f>
         <v/>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="4">
         <f>'IS'!G3*'Assumptions'!G29*'Assumptions'!$C$59</f>
         <v/>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="4">
         <f>'IS'!H3*'Assumptions'!H29*'Assumptions'!$C$59</f>
         <v/>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="4">
         <f>'IS'!I3*'Assumptions'!I29*'Assumptions'!$C$59</f>
         <v/>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="4">
         <f>'IS'!J3*'Assumptions'!J29*'Assumptions'!$C$59</f>
         <v/>
       </c>
@@ -6574,23 +6578,23 @@
           <t>Depreciation of PP&amp;E (rate on opening balance)</t>
         </is>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="4">
         <f>'Schedules'!F11*'Assumptions'!$C$37</f>
         <v/>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="4">
         <f>'Schedules'!G11*'Assumptions'!$C$37</f>
         <v/>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="4">
         <f>'Schedules'!H11*'Assumptions'!$C$37</f>
         <v/>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="4">
         <f>'Schedules'!I11*'Assumptions'!$C$37</f>
         <v/>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="4">
         <f>'Schedules'!J11*'Assumptions'!$C$37</f>
         <v/>
       </c>
@@ -6601,23 +6605,23 @@
           <t>Closing PP&amp;E</t>
         </is>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="4">
         <f>'Schedules'!F11+'Schedules'!F12-'Schedules'!F13</f>
         <v/>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="4">
         <f>'Schedules'!G11+'Schedules'!G12-'Schedules'!G13</f>
         <v/>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="4">
         <f>'Schedules'!H11+'Schedules'!H12-'Schedules'!H13</f>
         <v/>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="4">
         <f>'Schedules'!I11+'Schedules'!I12-'Schedules'!I13</f>
         <v/>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="4">
         <f>'Schedules'!J11+'Schedules'!J12-'Schedules'!J13</f>
         <v/>
       </c>
@@ -6635,23 +6639,23 @@
           <t>Opening intangibles</t>
         </is>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="4">
         <f>'Historicals'!E22</f>
         <v/>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="4">
         <f>'Schedules'!F20</f>
         <v/>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="4">
         <f>'Schedules'!G20</f>
         <v/>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="4">
         <f>'Schedules'!H20</f>
         <v/>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="4">
         <f>'Schedules'!I20</f>
         <v/>
       </c>
@@ -6662,23 +6666,23 @@
           <t>Intangible additions (revenue x total capex % x intangible share)</t>
         </is>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="4">
         <f>'IS'!F3*'Assumptions'!F29*'Assumptions'!$C$58</f>
         <v/>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="4">
         <f>'IS'!G3*'Assumptions'!G29*'Assumptions'!$C$58</f>
         <v/>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="4">
         <f>'IS'!H3*'Assumptions'!H29*'Assumptions'!$C$58</f>
         <v/>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="4">
         <f>'IS'!I3*'Assumptions'!I29*'Assumptions'!$C$58</f>
         <v/>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="4">
         <f>'IS'!J3*'Assumptions'!J29*'Assumptions'!$C$58</f>
         <v/>
       </c>
@@ -6689,23 +6693,23 @@
           <t>Amortisation (rate on opening balance)</t>
         </is>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="4">
         <f>'Schedules'!F17*'Assumptions'!$C$60</f>
         <v/>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="4">
         <f>'Schedules'!G17*'Assumptions'!$C$60</f>
         <v/>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="4">
         <f>'Schedules'!H17*'Assumptions'!$C$60</f>
         <v/>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="4">
         <f>'Schedules'!I17*'Assumptions'!$C$60</f>
         <v/>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="4">
         <f>'Schedules'!J17*'Assumptions'!$C$60</f>
         <v/>
       </c>
@@ -6716,23 +6720,23 @@
           <t>Closing intangibles</t>
         </is>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="4">
         <f>'Schedules'!F17+'Schedules'!F18-'Schedules'!F19</f>
         <v/>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="4">
         <f>'Schedules'!G17+'Schedules'!G18-'Schedules'!G19</f>
         <v/>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="4">
         <f>'Schedules'!H17+'Schedules'!H18-'Schedules'!H19</f>
         <v/>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="4">
         <f>'Schedules'!I17+'Schedules'!I18-'Schedules'!I19</f>
         <v/>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="4">
         <f>'Schedules'!J17+'Schedules'!J18-'Schedules'!J19</f>
         <v/>
       </c>
@@ -6743,23 +6747,23 @@
           <t>Total cash capex (PP&amp;E + intangible)</t>
         </is>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="4">
         <f>'Schedules'!F12+'Schedules'!F18</f>
         <v/>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="4">
         <f>'Schedules'!G12+'Schedules'!G18</f>
         <v/>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="4">
         <f>'Schedules'!H12+'Schedules'!H18</f>
         <v/>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="4">
         <f>'Schedules'!I12+'Schedules'!I18</f>
         <v/>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="4">
         <f>'Schedules'!J12+'Schedules'!J18</f>
         <v/>
       </c>
@@ -6777,23 +6781,23 @@
           <t>Opening right-of-use assets</t>
         </is>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="4">
         <f>'Historicals'!E21</f>
         <v/>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="4">
         <f>'Schedules'!F27</f>
         <v/>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="4">
         <f>'Schedules'!G27</f>
         <v/>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="4">
         <f>'Schedules'!H27</f>
         <v/>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="4">
         <f>'Schedules'!I27</f>
         <v/>
       </c>
@@ -6804,23 +6808,23 @@
           <t>New ROU asset additions (revenue x ROU additions %)</t>
         </is>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="4">
         <f>'IS'!F3*'Assumptions'!F30</f>
         <v/>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="4">
         <f>'IS'!G3*'Assumptions'!G30</f>
         <v/>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="4">
         <f>'IS'!H3*'Assumptions'!H30</f>
         <v/>
       </c>
-      <c r="I25" s="3">
+      <c r="I25" s="4">
         <f>'IS'!I3*'Assumptions'!I30</f>
         <v/>
       </c>
-      <c r="J25" s="3">
+      <c r="J25" s="4">
         <f>'IS'!J3*'Assumptions'!J30</f>
         <v/>
       </c>
@@ -6831,23 +6835,23 @@
           <t>Depreciation of ROU assets (rate on opening balance)</t>
         </is>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="4">
         <f>'Schedules'!F24*'Assumptions'!$C$38</f>
         <v/>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="4">
         <f>'Schedules'!G24*'Assumptions'!$C$38</f>
         <v/>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="4">
         <f>'Schedules'!H24*'Assumptions'!$C$38</f>
         <v/>
       </c>
-      <c r="I26" s="3">
+      <c r="I26" s="4">
         <f>'Schedules'!I24*'Assumptions'!$C$38</f>
         <v/>
       </c>
-      <c r="J26" s="3">
+      <c r="J26" s="4">
         <f>'Schedules'!J24*'Assumptions'!$C$38</f>
         <v/>
       </c>
@@ -6858,23 +6862,23 @@
           <t>Closing right-of-use assets</t>
         </is>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="4">
         <f>'Schedules'!F24+'Schedules'!F25-'Schedules'!F26</f>
         <v/>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="4">
         <f>'Schedules'!G24+'Schedules'!G25-'Schedules'!G26</f>
         <v/>
       </c>
-      <c r="H27" s="3">
+      <c r="H27" s="4">
         <f>'Schedules'!H24+'Schedules'!H25-'Schedules'!H26</f>
         <v/>
       </c>
-      <c r="I27" s="3">
+      <c r="I27" s="4">
         <f>'Schedules'!I24+'Schedules'!I25-'Schedules'!I26</f>
         <v/>
       </c>
-      <c r="J27" s="3">
+      <c r="J27" s="4">
         <f>'Schedules'!J24+'Schedules'!J25-'Schedules'!J26</f>
         <v/>
       </c>
@@ -6885,23 +6889,23 @@
           <t>Opening lease liabilities</t>
         </is>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="4">
         <f>'Historicals'!E30</f>
         <v/>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="4">
         <f>'Schedules'!F31</f>
         <v/>
       </c>
-      <c r="H28" s="3">
+      <c r="H28" s="4">
         <f>'Schedules'!G31</f>
         <v/>
       </c>
-      <c r="I28" s="3">
+      <c r="I28" s="4">
         <f>'Schedules'!H31</f>
         <v/>
       </c>
-      <c r="J28" s="3">
+      <c r="J28" s="4">
         <f>'Schedules'!I31</f>
         <v/>
       </c>
@@ -6912,23 +6916,23 @@
           <t>Lease interest (discount rate on opening liability)</t>
         </is>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="4">
         <f>'Schedules'!F28*'Assumptions'!$C$53</f>
         <v/>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="4">
         <f>'Schedules'!G28*'Assumptions'!$C$53</f>
         <v/>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="4">
         <f>'Schedules'!H28*'Assumptions'!$C$53</f>
         <v/>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="4">
         <f>'Schedules'!I28*'Assumptions'!$C$53</f>
         <v/>
       </c>
-      <c r="J29" s="3">
+      <c r="J29" s="4">
         <f>'Schedules'!J28*'Assumptions'!$C$53</f>
         <v/>
       </c>
@@ -6939,23 +6943,23 @@
           <t>Lease principal repaid (opening / implied term + additions x fit rate)</t>
         </is>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="4">
         <f>'Schedules'!F28/'Assumptions'!$C$56+'Schedules'!F25*'Assumptions'!$C$57</f>
         <v/>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="4">
         <f>'Schedules'!G28/'Assumptions'!$C$56+'Schedules'!G25*'Assumptions'!$C$57</f>
         <v/>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="4">
         <f>'Schedules'!H28/'Assumptions'!$C$56+'Schedules'!H25*'Assumptions'!$C$57</f>
         <v/>
       </c>
-      <c r="I30" s="3">
+      <c r="I30" s="4">
         <f>'Schedules'!I28/'Assumptions'!$C$56+'Schedules'!I25*'Assumptions'!$C$57</f>
         <v/>
       </c>
-      <c r="J30" s="3">
+      <c r="J30" s="4">
         <f>'Schedules'!J28/'Assumptions'!$C$56+'Schedules'!J25*'Assumptions'!$C$57</f>
         <v/>
       </c>
@@ -6966,23 +6970,23 @@
           <t>Closing lease liabilities</t>
         </is>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="4">
         <f>'Schedules'!F28+'Schedules'!F25-'Schedules'!F30</f>
         <v/>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="4">
         <f>'Schedules'!G28+'Schedules'!G25-'Schedules'!G30</f>
         <v/>
       </c>
-      <c r="H31" s="3">
+      <c r="H31" s="4">
         <f>'Schedules'!H28+'Schedules'!H25-'Schedules'!H30</f>
         <v/>
       </c>
-      <c r="I31" s="3">
+      <c r="I31" s="4">
         <f>'Schedules'!I28+'Schedules'!I25-'Schedules'!I30</f>
         <v/>
       </c>
-      <c r="J31" s="3">
+      <c r="J31" s="4">
         <f>'Schedules'!J28+'Schedules'!J25-'Schedules'!J30</f>
         <v/>
       </c>
@@ -7000,23 +7004,23 @@
           <t>Dividends declared (payout ratio on net income, floored at nil)</t>
         </is>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="4">
         <f>MAX('IS'!F17,0)*'Assumptions'!$C$40</f>
         <v/>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="4">
         <f>MAX('IS'!G17,0)*'Assumptions'!$C$40</f>
         <v/>
       </c>
-      <c r="H34" s="3">
+      <c r="H34" s="4">
         <f>MAX('IS'!H17,0)*'Assumptions'!$C$40</f>
         <v/>
       </c>
-      <c r="I34" s="3">
+      <c r="I34" s="4">
         <f>MAX('IS'!I17,0)*'Assumptions'!$C$40</f>
         <v/>
       </c>
-      <c r="J34" s="3">
+      <c r="J34" s="4">
         <f>MAX('IS'!J17,0)*'Assumptions'!$C$40</f>
         <v/>
       </c>
@@ -7027,23 +7031,23 @@
           <t>Opening shareholders' equity</t>
         </is>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="4">
         <f>'Historicals'!E33</f>
         <v/>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="4">
         <f>'Schedules'!F36</f>
         <v/>
       </c>
-      <c r="H35" s="3">
+      <c r="H35" s="4">
         <f>'Schedules'!G36</f>
         <v/>
       </c>
-      <c r="I35" s="3">
+      <c r="I35" s="4">
         <f>'Schedules'!H36</f>
         <v/>
       </c>
-      <c r="J35" s="3">
+      <c r="J35" s="4">
         <f>'Schedules'!I36</f>
         <v/>
       </c>
@@ -7054,23 +7058,23 @@
           <t>Closing shareholders' equity</t>
         </is>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="4">
         <f>'Schedules'!F35+'IS'!F17-'Schedules'!F34</f>
         <v/>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="4">
         <f>'Schedules'!G35+'IS'!G17-'Schedules'!G34</f>
         <v/>
       </c>
-      <c r="H36" s="3">
+      <c r="H36" s="4">
         <f>'Schedules'!H35+'IS'!H17-'Schedules'!H34</f>
         <v/>
       </c>
-      <c r="I36" s="3">
+      <c r="I36" s="4">
         <f>'Schedules'!I35+'IS'!I17-'Schedules'!I34</f>
         <v/>
       </c>
-      <c r="J36" s="3">
+      <c r="J36" s="4">
         <f>'Schedules'!J35+'IS'!J17-'Schedules'!J34</f>
         <v/>
       </c>
@@ -7088,23 +7092,23 @@
           <t>Cash generated before financing</t>
         </is>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="4">
         <f>'IS'!F7-'Schedules'!F8-'Schedules'!F21-'Schedules'!F30-'Schedules'!F29-'IS'!F16-'Schedules'!F34</f>
         <v/>
       </c>
-      <c r="G39" s="3">
+      <c r="G39" s="4">
         <f>'IS'!G7-'Schedules'!G8-'Schedules'!G21-'Schedules'!G30-'Schedules'!G29-'IS'!G16-'Schedules'!G34</f>
         <v/>
       </c>
-      <c r="H39" s="3">
+      <c r="H39" s="4">
         <f>'IS'!H7-'Schedules'!H8-'Schedules'!H21-'Schedules'!H30-'Schedules'!H29-'IS'!H16-'Schedules'!H34</f>
         <v/>
       </c>
-      <c r="I39" s="3">
+      <c r="I39" s="4">
         <f>'IS'!I7-'Schedules'!I8-'Schedules'!I21-'Schedules'!I30-'Schedules'!I29-'IS'!I16-'Schedules'!I34</f>
         <v/>
       </c>
-      <c r="J39" s="3">
+      <c r="J39" s="4">
         <f>'IS'!J7-'Schedules'!J8-'Schedules'!J21-'Schedules'!J30-'Schedules'!J29-'IS'!J16-'Schedules'!J34</f>
         <v/>
       </c>
@@ -7115,23 +7119,23 @@
           <t>Opening borrowings</t>
         </is>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="4">
         <f>'Historicals'!E31</f>
         <v/>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="4">
         <f>'Schedules'!F47</f>
         <v/>
       </c>
-      <c r="H40" s="3">
+      <c r="H40" s="4">
         <f>'Schedules'!G47</f>
         <v/>
       </c>
-      <c r="I40" s="3">
+      <c r="I40" s="4">
         <f>'Schedules'!H47</f>
         <v/>
       </c>
-      <c r="J40" s="3">
+      <c r="J40" s="4">
         <f>'Schedules'!I47</f>
         <v/>
       </c>
@@ -7142,23 +7146,23 @@
           <t>Opening cash</t>
         </is>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="4">
         <f>'Historicals'!E25</f>
         <v/>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="4">
         <f>'Schedules'!F48</f>
         <v/>
       </c>
-      <c r="H41" s="3">
+      <c r="H41" s="4">
         <f>'Schedules'!G48</f>
         <v/>
       </c>
-      <c r="I41" s="3">
+      <c r="I41" s="4">
         <f>'Schedules'!H48</f>
         <v/>
       </c>
-      <c r="J41" s="3">
+      <c r="J41" s="4">
         <f>'Schedules'!I48</f>
         <v/>
       </c>
@@ -7169,23 +7173,23 @@
           <t>Cash available before interest</t>
         </is>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="4">
         <f>'Schedules'!F41+'Schedules'!F39</f>
         <v/>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="4">
         <f>'Schedules'!G41+'Schedules'!G39</f>
         <v/>
       </c>
-      <c r="H42" s="3">
+      <c r="H42" s="4">
         <f>'Schedules'!H41+'Schedules'!H39</f>
         <v/>
       </c>
-      <c r="I42" s="3">
+      <c r="I42" s="4">
         <f>'Schedules'!I41+'Schedules'!I39</f>
         <v/>
       </c>
-      <c r="J42" s="3">
+      <c r="J42" s="4">
         <f>'Schedules'!J41+'Schedules'!J39</f>
         <v/>
       </c>
@@ -7196,23 +7200,23 @@
           <t>Interest on borrowings (rate on opening debt)</t>
         </is>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="4">
         <f>'Schedules'!F40*'Assumptions'!$C$44</f>
         <v/>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="4">
         <f>'Schedules'!G40*'Assumptions'!$C$44</f>
         <v/>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="4">
         <f>'Schedules'!H40*'Assumptions'!$C$44</f>
         <v/>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="4">
         <f>'Schedules'!I40*'Assumptions'!$C$44</f>
         <v/>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="4">
         <f>'Schedules'!J40*'Assumptions'!$C$44</f>
         <v/>
       </c>
@@ -7223,23 +7227,23 @@
           <t>Cash available before debt service</t>
         </is>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="4">
         <f>'Schedules'!F42-'Schedules'!F43</f>
         <v/>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="4">
         <f>'Schedules'!G42-'Schedules'!G43</f>
         <v/>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="4">
         <f>'Schedules'!H42-'Schedules'!H43</f>
         <v/>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="4">
         <f>'Schedules'!I42-'Schedules'!I43</f>
         <v/>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="4">
         <f>'Schedules'!J42-'Schedules'!J43</f>
         <v/>
       </c>
@@ -7250,23 +7254,23 @@
           <t>Repayment of borrowings</t>
         </is>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="4">
         <f>MAX(0,MIN('Schedules'!F40,'Schedules'!F44-'Assumptions'!$C$41))</f>
         <v/>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="4">
         <f>MAX(0,MIN('Schedules'!G40,'Schedules'!G44-'Assumptions'!$C$41))</f>
         <v/>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="4">
         <f>MAX(0,MIN('Schedules'!H40,'Schedules'!H44-'Assumptions'!$C$41))</f>
         <v/>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="4">
         <f>MAX(0,MIN('Schedules'!I40,'Schedules'!I44-'Assumptions'!$C$41))</f>
         <v/>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="4">
         <f>MAX(0,MIN('Schedules'!J40,'Schedules'!J44-'Assumptions'!$C$41))</f>
         <v/>
       </c>
@@ -7277,23 +7281,23 @@
           <t>Revolver draw</t>
         </is>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="4">
         <f>MAX(0,'Assumptions'!$C$41-'Schedules'!F44)</f>
         <v/>
       </c>
-      <c r="G46" s="3">
+      <c r="G46" s="4">
         <f>MAX(0,'Assumptions'!$C$41-'Schedules'!G44)</f>
         <v/>
       </c>
-      <c r="H46" s="3">
+      <c r="H46" s="4">
         <f>MAX(0,'Assumptions'!$C$41-'Schedules'!H44)</f>
         <v/>
       </c>
-      <c r="I46" s="3">
+      <c r="I46" s="4">
         <f>MAX(0,'Assumptions'!$C$41-'Schedules'!I44)</f>
         <v/>
       </c>
-      <c r="J46" s="3">
+      <c r="J46" s="4">
         <f>MAX(0,'Assumptions'!$C$41-'Schedules'!J44)</f>
         <v/>
       </c>
@@ -7304,23 +7308,23 @@
           <t>Closing borrowings</t>
         </is>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="4">
         <f>'Schedules'!F40-'Schedules'!F45+'Schedules'!F46</f>
         <v/>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="4">
         <f>'Schedules'!G40-'Schedules'!G45+'Schedules'!G46</f>
         <v/>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="4">
         <f>'Schedules'!H40-'Schedules'!H45+'Schedules'!H46</f>
         <v/>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="4">
         <f>'Schedules'!I40-'Schedules'!I45+'Schedules'!I46</f>
         <v/>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="4">
         <f>'Schedules'!J40-'Schedules'!J45+'Schedules'!J46</f>
         <v/>
       </c>
@@ -7331,23 +7335,23 @@
           <t>Closing cash (debt schedule's own track)</t>
         </is>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="4">
         <f>'Schedules'!F44-'Schedules'!F45+'Schedules'!F46</f>
         <v/>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="4">
         <f>'Schedules'!G44-'Schedules'!G45+'Schedules'!G46</f>
         <v/>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="4">
         <f>'Schedules'!H44-'Schedules'!H45+'Schedules'!H46</f>
         <v/>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="4">
         <f>'Schedules'!I44-'Schedules'!I45+'Schedules'!I46</f>
         <v/>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="4">
         <f>'Schedules'!J44-'Schedules'!J45+'Schedules'!J46</f>
         <v/>
       </c>
@@ -7388,23 +7392,23 @@
       </c>
     </row>
     <row r="2">
-      <c r="F2" s="5">
+      <c r="F2" s="6">
         <f>'Assumptions'!F$2</f>
         <v/>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <f>'Assumptions'!G$2</f>
         <v/>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="6">
         <f>'Assumptions'!H$2</f>
         <v/>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="6">
         <f>'Assumptions'!I$2</f>
         <v/>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="6">
         <f>'Assumptions'!J$2</f>
         <v/>
       </c>
@@ -7415,7 +7419,7 @@
           <t>Cost of equity (CAPM: risk-free rate + beta x equity risk premium)</t>
         </is>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="10">
         <f>'Assumptions'!$C$45+'Assumptions'!$C$47*'Assumptions'!$C$46</f>
         <v/>
       </c>
@@ -7426,7 +7430,7 @@
           <t>After-tax cost of debt (blended rate x (1 - tax rate))</t>
         </is>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="10">
         <f>'Assumptions'!$C$61*(1-'Assumptions'!$C$39)</f>
         <v/>
       </c>
@@ -7437,7 +7441,7 @@
           <t>WACC</t>
         </is>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <f>(1-'Assumptions'!$C$48)*'DCF'!$C$3+'Assumptions'!$C$48*'DCF'!$C$4</f>
         <v/>
       </c>
@@ -7455,23 +7459,23 @@
           <t>EBIT (from the income statement)</t>
         </is>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <f>'IS'!F12</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="14">
         <f>'IS'!G12</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <f>'IS'!H12</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="14">
         <f>'IS'!I12</f>
         <v/>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="14">
         <f>'IS'!J12</f>
         <v/>
       </c>
@@ -7482,23 +7486,23 @@
           <t>EBIT after tax (unlevered: nothing below EBIT enters this sheet)</t>
         </is>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="4">
         <f>'DCF'!F8*(1-'Assumptions'!$C$39)</f>
         <v/>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="4">
         <f>'DCF'!G8*(1-'Assumptions'!$C$39)</f>
         <v/>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="4">
         <f>'DCF'!H8*(1-'Assumptions'!$C$39)</f>
         <v/>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="4">
         <f>'DCF'!I8*(1-'Assumptions'!$C$39)</f>
         <v/>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="4">
         <f>'DCF'!J8*(1-'Assumptions'!$C$39)</f>
         <v/>
       </c>
@@ -7509,23 +7513,23 @@
           <t>Depreciation and amortisation (added back)</t>
         </is>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="14">
         <f>'IS'!F11</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="14">
         <f>'IS'!G11</f>
         <v/>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="14">
         <f>'IS'!H11</f>
         <v/>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="14">
         <f>'IS'!I11</f>
         <v/>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="14">
         <f>'IS'!J11</f>
         <v/>
       </c>
@@ -7536,23 +7540,23 @@
           <t>Total cash capex (PP&amp;E + intangible)</t>
         </is>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <f>'Schedules'!F21</f>
         <v/>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="14">
         <f>'Schedules'!G21</f>
         <v/>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="14">
         <f>'Schedules'!H21</f>
         <v/>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="14">
         <f>'Schedules'!I21</f>
         <v/>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="14">
         <f>'Schedules'!J21</f>
         <v/>
       </c>
@@ -7563,23 +7567,23 @@
           <t>New ROU asset additions (an investing outflow — leases are debt here)</t>
         </is>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <f>'Schedules'!F25</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="14">
         <f>'Schedules'!G25</f>
         <v/>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="14">
         <f>'Schedules'!H25</f>
         <v/>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="14">
         <f>'Schedules'!I25</f>
         <v/>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="14">
         <f>'Schedules'!J25</f>
         <v/>
       </c>
@@ -7590,23 +7594,23 @@
           <t>Increase in net working capital</t>
         </is>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <f>'Schedules'!F8</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="14">
         <f>'Schedules'!G8</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="14">
         <f>'Schedules'!H8</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="14">
         <f>'Schedules'!I8</f>
         <v/>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="14">
         <f>'Schedules'!J8</f>
         <v/>
       </c>
@@ -7617,23 +7621,23 @@
           <t>Unlevered free cash flow</t>
         </is>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="4">
         <f>'DCF'!F9+'DCF'!F10-'DCF'!F11-'DCF'!F12-'DCF'!F13</f>
         <v/>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="4">
         <f>'DCF'!G9+'DCF'!G10-'DCF'!G11-'DCF'!G12-'DCF'!G13</f>
         <v/>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="4">
         <f>'DCF'!H9+'DCF'!H10-'DCF'!H11-'DCF'!H12-'DCF'!H13</f>
         <v/>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="4">
         <f>'DCF'!I9+'DCF'!I10-'DCF'!I11-'DCF'!I12-'DCF'!I13</f>
         <v/>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="4">
         <f>'DCF'!J9+'DCF'!J10-'DCF'!J11-'DCF'!J12-'DCF'!J13</f>
         <v/>
       </c>
@@ -7644,23 +7648,23 @@
           <t>Discount period (years, mid-year convention)</t>
         </is>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="13">
         <f>COLUMN()-COLUMN('DCF'!$F$14)+0.5</f>
         <v/>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="13">
         <f>COLUMN()-COLUMN('DCF'!$F$14)+0.5</f>
         <v/>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="13">
         <f>COLUMN()-COLUMN('DCF'!$F$14)+0.5</f>
         <v/>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="13">
         <f>COLUMN()-COLUMN('DCF'!$F$14)+0.5</f>
         <v/>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="13">
         <f>COLUMN()-COLUMN('DCF'!$F$14)+0.5</f>
         <v/>
       </c>
@@ -7671,23 +7675,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <f>(1+'DCF'!$C$5)^'DCF'!F15</f>
         <v/>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="13">
         <f>(1+'DCF'!$C$5)^'DCF'!G15</f>
         <v/>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="13">
         <f>(1+'DCF'!$C$5)^'DCF'!H15</f>
         <v/>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="13">
         <f>(1+'DCF'!$C$5)^'DCF'!I15</f>
         <v/>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="13">
         <f>(1+'DCF'!$C$5)^'DCF'!J15</f>
         <v/>
       </c>
@@ -7698,23 +7702,23 @@
           <t>PV of unlevered free cash flow</t>
         </is>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="4">
         <f>'DCF'!F14/'DCF'!F16</f>
         <v/>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="4">
         <f>'DCF'!G14/'DCF'!G16</f>
         <v/>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="4">
         <f>'DCF'!H14/'DCF'!H16</f>
         <v/>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="4">
         <f>'DCF'!I14/'DCF'!I16</f>
         <v/>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="4">
         <f>'DCF'!J14/'DCF'!J16</f>
         <v/>
       </c>
@@ -7739,7 +7743,7 @@
           <t>Perpetuity growth rate (g*)</t>
         </is>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="15">
         <f>'Assumptions'!$C$49</f>
         <v/>
       </c>
@@ -7750,7 +7754,7 @@
           <t>Terminal PP&amp;E / revenue (post-programme anchor)</t>
         </is>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="10">
         <f>('BS'!J3/'IS'!J3)/(1+'DCF'!$C$21)^(1/'Assumptions'!$C$37)</f>
         <v/>
       </c>
@@ -7761,7 +7765,7 @@
           <t>Terminal ROU assets / revenue (FY2025 actual)</t>
         </is>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="10">
         <f>'Historicals'!E21/'Historicals'!E3</f>
         <v/>
       </c>
@@ -7772,7 +7776,7 @@
           <t>Terminal total capex (% of revenue, sustaining, grossed up for intangibles)</t>
         </is>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="10">
         <f>'DCF'!$C$22*('DCF'!$C$21+'Assumptions'!$C$37)/(1+'DCF'!$C$21)/'Assumptions'!$C$59</f>
         <v/>
       </c>
@@ -7783,7 +7787,7 @@
           <t>Terminal ROU additions (% of revenue, sustaining)</t>
         </is>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="10">
         <f>'DCF'!$C$23*('DCF'!$C$21+'Assumptions'!$C$38)/(1+'DCF'!$C$21)</f>
         <v/>
       </c>
@@ -7794,7 +7798,7 @@
           <t>Terminal PP&amp;E depreciation (% of revenue)</t>
         </is>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="10">
         <f>'Assumptions'!$C$37*'DCF'!$C$22/(1+'DCF'!$C$21)</f>
         <v/>
       </c>
@@ -7805,7 +7809,7 @@
           <t>Terminal ROU depreciation (% of revenue)</t>
         </is>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="10">
         <f>'Assumptions'!$C$38*'DCF'!$C$23/(1+'DCF'!$C$21)</f>
         <v/>
       </c>
@@ -7816,7 +7820,7 @@
           <t>Terminal intangible additions (% of revenue)</t>
         </is>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="10">
         <f>'DCF'!$C$24*'Assumptions'!$C$58</f>
         <v/>
       </c>
@@ -7827,7 +7831,7 @@
           <t>Terminal amortisation (% of revenue)</t>
         </is>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="10">
         <f>'DCF'!$C$28*'Assumptions'!$C$60/('DCF'!$C$21+'Assumptions'!$C$60)</f>
         <v/>
       </c>
@@ -7838,7 +7842,7 @@
           <t>Terminal D&amp;A (% of revenue)</t>
         </is>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="10">
         <f>'DCF'!$C$26+'DCF'!$C$27+'DCF'!$C$29</f>
         <v/>
       </c>
@@ -7849,7 +7853,7 @@
           <t>Terminal net working capital (% of revenue, negative — payables dominate)</t>
         </is>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="10">
         <f>'Schedules'!J6/'IS'!J3</f>
         <v/>
       </c>
@@ -7860,7 +7864,7 @@
           <t>Terminal revenue (the FY2030 LEVEL, not FY2031's)</t>
         </is>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="14">
         <f>'IS'!J3</f>
         <v/>
       </c>
@@ -7871,7 +7875,7 @@
           <t>Terminal EBITDA margin (FY2030 gross margin less FY2030 opex ratio)</t>
         </is>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="10">
         <f>'Assumptions'!J27-'Assumptions'!J28</f>
         <v/>
       </c>
@@ -7882,7 +7886,7 @@
           <t>Terminal EBITDA (margin x revenue)</t>
         </is>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="4">
         <f>'DCF'!$C$33*'DCF'!$C$32</f>
         <v/>
       </c>
@@ -7893,7 +7897,7 @@
           <t>Terminal depreciation and amortisation</t>
         </is>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="4">
         <f>'DCF'!$C$30*'DCF'!$C$32</f>
         <v/>
       </c>
@@ -7904,7 +7908,7 @@
           <t>Terminal EBIT</t>
         </is>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="4">
         <f>'DCF'!$C$34-'DCF'!$C$35</f>
         <v/>
       </c>
@@ -7915,7 +7919,7 @@
           <t>Terminal total cash capex</t>
         </is>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="4">
         <f>'DCF'!$C$24*'DCF'!$C$32</f>
         <v/>
       </c>
@@ -7926,7 +7930,7 @@
           <t>Terminal ROU asset additions</t>
         </is>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="4">
         <f>'DCF'!$C$25*'DCF'!$C$32</f>
         <v/>
       </c>
@@ -7937,7 +7941,7 @@
           <t>Terminal increase in net working capital (negative = cash released)</t>
         </is>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="4">
         <f>'DCF'!$C$31*'DCF'!$C$21/(1+'DCF'!$C$21)*'DCF'!$C$32</f>
         <v/>
       </c>
@@ -7948,7 +7952,7 @@
           <t>Terminal unlevered free cash flow</t>
         </is>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="4">
         <f>'DCF'!$C$36*(1-'Assumptions'!$C$39)+'DCF'!$C$35-'DCF'!$C$37-'DCF'!$C$38-'DCF'!$C$39</f>
         <v/>
       </c>
@@ -7959,7 +7963,7 @@
           <t>Terminal D&amp;A / EBITDA (the capital intensity Comps prices)</t>
         </is>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="10">
         <f>'DCF'!$C$35/'DCF'!$C$34</f>
         <v/>
       </c>
@@ -7977,7 +7981,7 @@
           <t>Terminal value (Gordon growth)</t>
         </is>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="4">
         <f>'DCF'!$C$40*(1+'DCF'!$C$21)/('DCF'!$C$5-'DCF'!$C$21)</f>
         <v/>
       </c>
@@ -7988,7 +7992,7 @@
           <t>Excess PP&amp;E over the re-based base, at FY2029</t>
         </is>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="4">
         <f>'BS'!I3-'DCF'!$C$22*'IS'!I3</f>
         <v/>
       </c>
@@ -7999,7 +8003,7 @@
           <t>Decay factor x = (1 - PP&amp;E depreciation rate) / (1 + WACC)</t>
         </is>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="13">
         <f>(1-'Assumptions'!$C$37)/(1+'DCF'!$C$5)</f>
         <v/>
       </c>
@@ -8010,7 +8014,7 @@
           <t>Value at the terminal date of the excess PP&amp;E tax shield</t>
         </is>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="4">
         <f>'Assumptions'!$C$39*'Assumptions'!$C$37*'DCF'!$C$45*'DCF'!$C$46/(1-'DCF'!$C$46)</f>
         <v/>
       </c>
@@ -8021,7 +8025,7 @@
           <t>Terminal value (exit multiple)</t>
         </is>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="4">
         <f>'IS'!J7*'Assumptions'!$C$31</f>
         <v/>
       </c>
@@ -8039,7 +8043,7 @@
           <t>Memo: exit-multiple TV / terminal EBIT (equals the peer median EV/EBIT)</t>
         </is>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="5">
         <f>'DCF'!$C$48/'DCF'!$C$36</f>
         <v/>
       </c>
@@ -8050,7 +8054,7 @@
           <t>Memo: peer median EV/EBIT from Comps (the row above, to 2dp rounding)</t>
         </is>
       </c>
-      <c r="C51" s="15">
+      <c r="C51" s="16">
         <f>'Comps'!$J$18</f>
         <v/>
       </c>
@@ -8061,7 +8065,7 @@
           <t>Gordon terminal value / terminal EBITDA (the multiple Gordon implies)</t>
         </is>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="5">
         <f>'DCF'!$C$44/'DCF'!$C$34</f>
         <v/>
       </c>
@@ -8072,7 +8076,7 @@
           <t>Gordon terminal value / terminal EBIT (the like-for-like peer comparison)</t>
         </is>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="5">
         <f>'DCF'!$C$44/'DCF'!$C$36</f>
         <v/>
       </c>
@@ -8097,7 +8101,7 @@
           <t>PV of the explicit forecast period</t>
         </is>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="4">
         <f>'DCF'!F17+'DCF'!G17+'DCF'!H17+'DCF'!I17+'DCF'!J17</f>
         <v/>
       </c>
@@ -8108,7 +8112,7 @@
           <t>PV of the terminal value (Gordon plus the excess PP&amp;E shield)</t>
         </is>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="4">
         <f>('DCF'!$C$44+'DCF'!$C$47)/'DCF'!J16</f>
         <v/>
       </c>
@@ -8119,7 +8123,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="4">
         <f>'DCF'!$C$57+'DCF'!$C$58</f>
         <v/>
       </c>
@@ -8130,7 +8134,7 @@
           <t>Terminal value as a share of enterprise value</t>
         </is>
       </c>
-      <c r="C60" s="9">
+      <c r="C60" s="10">
         <f>'DCF'!$C$58/'DCF'!$C$59</f>
         <v/>
       </c>
@@ -8141,7 +8145,7 @@
           <t>Net debt at FY2025 (borrowings less cash, excluding leases)</t>
         </is>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="4">
         <f>'Historicals'!E31-'Historicals'!E25</f>
         <v/>
       </c>
@@ -8152,7 +8156,7 @@
           <t>Lease liabilities at FY2025 (deducted as debt, as in the WACC weight)</t>
         </is>
       </c>
-      <c r="C62" s="13">
+      <c r="C62" s="14">
         <f>'Historicals'!E30</f>
         <v/>
       </c>
@@ -8163,7 +8167,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="4">
         <f>'DCF'!$C$59-'DCF'!$C$61-'DCF'!$C$62</f>
         <v/>
       </c>
@@ -8174,7 +8178,7 @@
           <t>Shares in issue (weighted average diluted, m)</t>
         </is>
       </c>
-      <c r="C64" s="16">
+      <c r="C64" s="17">
         <f>'Historicals'!E44</f>
         <v/>
       </c>
@@ -8185,7 +8189,7 @@
           <t>Implied share price (p)</t>
         </is>
       </c>
-      <c r="C65" s="17">
+      <c r="C65" s="18">
         <f>'DCF'!$C$63/'DCF'!$C$64*100</f>
         <v/>
       </c>
@@ -8196,7 +8200,7 @@
           <t>Implied share price against the traded price on Comps</t>
         </is>
       </c>
-      <c r="C66" s="9">
+      <c r="C66" s="10">
         <f>'DCF'!$C$65/'Comps'!$C$24-1</f>
         <v/>
       </c>

--- a/dist/greggs_model.xlsx
+++ b/dist/greggs_model.xlsx
@@ -638,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -691,10 +691,31 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="75" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>The risk-free rate, equity risk premium, beta and RCF credit spread are reasoned judgement estimates, not sourced figures. Every other input is either transcribed from a filing (see Historicals, column L) or derived from those transcriptions.</t>
+          <t>LEASE TREATMENT: post-IFRS 16 throughout, and applied identically to the DCF, the trading comps and the LBO so the three can be read against each other. EBITDA excludes rent; right-of-use depreciation sits inside D&amp;A; new right-of-use additions are an investing outflow in unlevered free cash flow; and lease liabilities are deducted as debt in the equity bridge and carried in the debt weight of the WACC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>PROVENANCE IS NOT SYMMETRIC. Greggs' own historical figures were read line by line from the annual reports and reconciled to the filings, each with a page reference (Historicals, column L). The peer figures were not: they came from results announcements, carry no page references, and three of the five peer EBITDAs are build-ups from printed components rather than printed subtotals. The load-bearing statistic — the peer median EV/EBIT — rests only on printed EBIT figures. See Comps for the detail; the two sets are in one table but are not of one standard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>IMPAIRMENT CONVENTION: the historical depreciation lines include the year's net impairment, so D&amp;A here exceeds the cash flow statement's depreciation by £3.9-6.9m a year and impairment is added back as the non-cash charge it is. One consequence is disclosed on Comps: Greggs' EBIT is struck after impairment while every peer's underlying EBIT is struck before it, so the headline EV/EBIT comparison is not like for like. Comps carries the restated, like-for-like version beside it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVERYTHING HERE IS SOURCED. The risk-free rate, equity risk premium, beta and RCF credit spread are reasoned judgement estimates; so are the £50m minimum cash floor and the LBO's 4.0x entry leverage and 20% IRR hurdle, which are conventions rather than facts. Market data — every share price, share count and the 52-week range — is a one-day observation from a price provider, not a filing. The forecast drivers are the author's assumptions and are not company guidance. Everything else is transcribed from a filing (see Historicals, column L) or derived from those transcriptions.</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2250,7 @@
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>The median of five observations IS one observation — here J D Wetherspoon, a majority-freehold pub company. Dropping any of the three highest names moves the EV/EBIT median about -4.6%, which is the honest error bar on everything derived from it.</t>
+          <t>The median of five observations IS one observation — here J D Wetherspoon, a majority-freehold pub company. Dropping any of the three highest names moves the EV/EBIT median by -4.6% (SSP or Whitbread) or -4.5% (JDW, which IS the median), which is the honest error bar on everything derived from it.</t>
         </is>
       </c>
     </row>
@@ -3101,11 +3122,11 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>No forecast revenue growth outside +/-50%</t>
+          <t>No forecast revenue growth outside +/-50%, including the step off the last reported year</t>
         </is>
       </c>
       <c r="D9" s="3">
-        <f>AND(ABS('IS'!G3/'IS'!F3-1)&lt;0.5,ABS('IS'!H3/'IS'!G3-1)&lt;0.5,ABS('IS'!I3/'IS'!H3-1)&lt;0.5,ABS('IS'!J3/'IS'!I3-1)&lt;0.5)</f>
+        <f>AND(ABS('IS'!F3/'Historicals'!E3-1)&lt;0.5,ABS('IS'!G3/'IS'!F3-1)&lt;0.5,ABS('IS'!H3/'IS'!G3-1)&lt;0.5,ABS('IS'!I3/'IS'!H3-1)&lt;0.5,ABS('IS'!J3/'IS'!I3-1)&lt;0.5)</f>
         <v/>
       </c>
     </row>
@@ -3130,7 +3151,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Peak forecast borrowings (£m) — against the £100m facility drawn at FY2025</t>
+          <t>Peak forecast borrowings (£m) — against the £100m facility Greggs drew on at FY2025 (£25.0m drawn of £100m available)</t>
         </is>
       </c>
       <c r="C13" s="4">
